--- a/v1/data/table-books.xlsx
+++ b/v1/data/table-books.xlsx
@@ -91,15 +91,15 @@
     <t xml:space="preserve">Zon</t>
   </si>
   <si>
+    <t xml:space="preserve">Leo</t>
+  </si>
+  <si>
     <t xml:space="preserve">^Bero^</t>
   </si>
   <si>
     <t xml:space="preserve">Pom</t>
   </si>
   <si>
-    <t xml:space="preserve">Leo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lan</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t xml:space="preserve">^TCDLand2^</t>
   </si>
   <si>
+    <t xml:space="preserve">Bad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">^Bra^</t>
+  </si>
+  <si>
     <t xml:space="preserve">^MiscDC^</t>
   </si>
   <si>
-    <t xml:space="preserve">Bad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">^Bra^</t>
+    <t xml:space="preserve">Sct</t>
   </si>
   <si>
     <t xml:space="preserve">^Sul^</t>
   </si>
   <si>
-    <t xml:space="preserve">Sct</t>
-  </si>
-  <si>
     <t xml:space="preserve">^MiscBon^</t>
   </si>
   <si>
@@ -217,15 +217,15 @@
     <t xml:space="preserve">Far</t>
   </si>
   <si>
+    <t xml:space="preserve">Sch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mat</t>
+  </si>
+  <si>
     <t xml:space="preserve">Min</t>
   </si>
   <si>
-    <t xml:space="preserve">Sch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mat</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rue</t>
   </si>
   <si>
@@ -271,13 +271,13 @@
     <t xml:space="preserve">CN</t>
   </si>
   <si>
+    <t xml:space="preserve">Lwg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kap</t>
   </si>
   <si>
     <t xml:space="preserve">^Hen^</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lwg</t>
   </si>
   <si>
     <t xml:space="preserve">Sab</t>
@@ -1010,14 +1010,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD8D8D8"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -1084,15 +1084,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1112,19 +1112,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1491,10 +1491,10 @@
       <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="5" t="s">
@@ -1509,10 +1509,10 @@
       <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="7" t="s">
@@ -1521,13 +1521,13 @@
       <c r="AG1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="8" t="s">
+      <c r="AH1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AI1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="9" t="s">
@@ -1542,46 +1542,46 @@
       <c r="AN1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AO1" s="8" t="s">
         <v>40</v>
       </c>
       <c r="AP1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AS1" s="8" t="s">
         <v>44</v>
       </c>
       <c r="AT1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AU1" s="8" t="s">
         <v>46</v>
       </c>
       <c r="AV1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="8" t="s">
+      <c r="AW1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="8" t="s">
+      <c r="AX1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="8" t="s">
+      <c r="AY1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="8" t="s">
+      <c r="AZ1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="8" t="s">
+      <c r="BA1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BB1" s="8" t="s">
         <v>53</v>
       </c>
       <c r="BC1" s="5" t="s">
@@ -1590,7 +1590,7 @@
       <c r="BD1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="8" t="s">
+      <c r="BE1" s="7" t="s">
         <v>56</v>
       </c>
       <c r="BF1" s="5" t="s">
@@ -1629,13 +1629,13 @@
       <c r="BQ1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BR1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="7" t="s">
+      <c r="BS1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="7" t="s">
+      <c r="BT1" s="6" t="s">
         <v>71</v>
       </c>
       <c r="BU1" s="5" t="s">
@@ -1674,10 +1674,10 @@
       <c r="CF1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="4" t="s">
+      <c r="CG1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="5" t="s">
+      <c r="CH1" s="4" t="s">
         <v>85</v>
       </c>
       <c r="CI1" s="5" t="s">
@@ -1701,10 +1701,10 @@
       <c r="CO1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="7" t="s">
+      <c r="CP1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="7" t="s">
+      <c r="CQ1" s="6" t="s">
         <v>94</v>
       </c>
       <c r="CR1" s="5" t="s">
@@ -1814,14 +1814,14 @@
       <c r="W2" s="12" t="n">
         <v>161</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="Y2" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Y2" s="12" t="n">
+      <c r="Z2" s="12" t="n">
         <v>182</v>
-      </c>
-      <c r="Z2" s="12" t="n">
-        <v>184</v>
       </c>
       <c r="AA2" s="12" t="n">
         <v>235</v>
@@ -1832,54 +1832,54 @@
       <c r="AC2" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AD2" s="14" t="s">
+      <c r="AD2" s="12" t="n">
+        <v>224</v>
+      </c>
+      <c r="AE2" s="14" t="n">
+        <v>161</v>
+      </c>
+      <c r="AF2" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="AG2" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AE2" s="12" t="n">
-        <v>224</v>
-      </c>
-      <c r="AF2" s="15" t="n">
-        <v>161</v>
-      </c>
-      <c r="AG2" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AH2" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="AI2" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AI2" s="12" t="n">
-        <v>184</v>
-      </c>
       <c r="AJ2" s="16"/>
-      <c r="AK2" s="14" t="s">
+      <c r="AK2" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AL2" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM2" s="13" t="s">
         <v>128</v>
       </c>
       <c r="AN2" s="16"/>
-      <c r="AO2" s="14" t="s">
+      <c r="AO2" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP2" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="AQ2" s="14" t="s">
+      <c r="AQ2" s="15" t="s">
         <v>129</v>
       </c>
       <c r="AR2" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="AS2" s="14" t="s">
+      <c r="AS2" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AT2" s="12" t="n">
         <v>166</v>
       </c>
-      <c r="AU2" s="14" t="s">
+      <c r="AU2" s="15" t="s">
         <v>130</v>
       </c>
       <c r="AV2" s="12" t="n">
@@ -1898,7 +1898,7 @@
       <c r="BA2" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="BB2" s="14" t="s">
+      <c r="BB2" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC2" s="12" t="n">
@@ -1933,22 +1933,22 @@
         <v>97</v>
       </c>
       <c r="BN2" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="BO2" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="BP2" s="12" t="n">
         <v>106</v>
-      </c>
-      <c r="BO2" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="BP2" s="12" t="n">
-        <v>142</v>
       </c>
       <c r="BQ2" s="12" t="n">
         <v>166</v>
       </c>
       <c r="BR2" s="16"/>
-      <c r="BS2" s="15" t="n">
+      <c r="BS2" s="14" t="n">
         <v>108</v>
       </c>
-      <c r="BT2" s="15" t="n">
+      <c r="BT2" s="14" t="n">
         <v>151</v>
       </c>
       <c r="BU2" s="12" t="n">
@@ -1985,13 +1985,13 @@
         <v>110</v>
       </c>
       <c r="CF2" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="CG2" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="CG2" s="13" t="s">
+      <c r="CH2" s="13" t="s">
         <v>138</v>
-      </c>
-      <c r="CH2" s="12" t="n">
-        <v>120</v>
       </c>
       <c r="CJ2" s="12" t="n">
         <v>129</v>
@@ -2011,7 +2011,7 @@
       <c r="CO2" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="CP2" s="15" t="n">
+      <c r="CP2" s="14" t="n">
         <v>72</v>
       </c>
       <c r="CQ2" s="17"/>
@@ -2135,14 +2135,14 @@
       <c r="W3" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="X3" s="13" t="s">
+      <c r="X3" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="Y3" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Y3" s="12" t="n">
+      <c r="Z3" s="12" t="n">
         <v>111</v>
-      </c>
-      <c r="Z3" s="12" t="n">
-        <v>94</v>
       </c>
       <c r="AA3" s="12" t="n">
         <v>132</v>
@@ -2153,50 +2153,50 @@
       <c r="AC3" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="AD3" s="16"/>
-      <c r="AE3" s="12" t="n">
+      <c r="AD3" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="AF3" s="15" t="n">
+      <c r="AE3" s="14" t="n">
         <v>121</v>
       </c>
-      <c r="AG3" s="13" t="s">
+      <c r="AF3" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="AH3" s="13" t="s">
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="AI3" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="AI3" s="12" t="n">
-        <v>108</v>
       </c>
       <c r="AJ3" s="16"/>
       <c r="AK3" s="16"/>
-      <c r="AL3" s="14" t="s">
+      <c r="AL3" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM3" s="13" t="s">
         <v>156</v>
       </c>
       <c r="AN3" s="16"/>
-      <c r="AO3" s="14" t="s">
+      <c r="AO3" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP3" s="12" t="n">
         <v>167</v>
       </c>
-      <c r="AQ3" s="14" t="s">
+      <c r="AQ3" s="15" t="s">
         <v>157</v>
       </c>
       <c r="AR3" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="AS3" s="14" t="s">
+      <c r="AS3" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AT3" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="AU3" s="14" t="s">
+      <c r="AU3" s="15" t="s">
         <v>158</v>
       </c>
       <c r="AV3" s="12" t="n">
@@ -2215,7 +2215,7 @@
       <c r="BA3" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="BB3" s="14" t="s">
+      <c r="BB3" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC3" s="12" t="n">
@@ -2250,22 +2250,22 @@
         <v>79</v>
       </c>
       <c r="BN3" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="BO3" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="BP3" s="12" t="n">
         <v>92</v>
-      </c>
-      <c r="BO3" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="BP3" s="12" t="n">
-        <v>96</v>
       </c>
       <c r="BQ3" s="12" t="n">
         <v>75</v>
       </c>
       <c r="BR3" s="16"/>
-      <c r="BS3" s="15" t="n">
+      <c r="BS3" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="BT3" s="15" t="n">
+      <c r="BT3" s="14" t="n">
         <v>101</v>
       </c>
       <c r="BU3" s="12" t="n">
@@ -2302,13 +2302,13 @@
         <v>107</v>
       </c>
       <c r="CF3" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="CG3" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="CG3" s="13" t="s">
+      <c r="CH3" s="13" t="s">
         <v>165</v>
-      </c>
-      <c r="CH3" s="12" t="n">
-        <v>103</v>
       </c>
       <c r="CJ3" s="12" t="n">
         <v>113</v>
@@ -2328,7 +2328,7 @@
       <c r="CO3" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="CP3" s="15" t="n">
+      <c r="CP3" s="14" t="n">
         <v>71</v>
       </c>
       <c r="CQ3" s="17"/>
@@ -2452,14 +2452,14 @@
       <c r="W4" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="X4" s="13" t="s">
+      <c r="X4" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="Y4" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Y4" s="12" t="n">
+      <c r="Z4" s="12" t="n">
         <v>142</v>
-      </c>
-      <c r="Z4" s="12" t="n">
-        <v>105</v>
       </c>
       <c r="AA4" s="12" t="n">
         <v>124</v>
@@ -2470,38 +2470,38 @@
       <c r="AC4" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="AD4" s="16"/>
-      <c r="AE4" s="12" t="n">
+      <c r="AD4" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="AF4" s="15" t="n">
+      <c r="AE4" s="14" t="n">
         <v>141</v>
       </c>
-      <c r="AG4" s="13" t="s">
+      <c r="AF4" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AH4" s="13" t="s">
+      <c r="AG4" s="16"/>
+      <c r="AH4" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="AI4" s="13" t="s">
         <v>180</v>
-      </c>
-      <c r="AI4" s="12" t="n">
-        <v>106</v>
       </c>
       <c r="AJ4" s="16"/>
       <c r="AK4" s="16"/>
-      <c r="AL4" s="14" t="s">
+      <c r="AL4" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM4" s="13" t="s">
         <v>181</v>
       </c>
       <c r="AN4" s="16"/>
-      <c r="AO4" s="14" t="s">
+      <c r="AO4" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP4" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="AQ4" s="14" t="s">
+      <c r="AQ4" s="15" t="s">
         <v>182</v>
       </c>
       <c r="AR4" s="12" t="n">
@@ -2511,7 +2511,7 @@
       <c r="AT4" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="AU4" s="14" t="s">
+      <c r="AU4" s="15" t="s">
         <v>152</v>
       </c>
       <c r="AV4" s="12" t="n">
@@ -2530,7 +2530,7 @@
       <c r="BA4" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="BB4" s="14" t="s">
+      <c r="BB4" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC4" s="12" t="n">
@@ -2565,22 +2565,22 @@
         <v>91</v>
       </c>
       <c r="BN4" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="BO4" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="BP4" s="12" t="n">
         <v>110</v>
-      </c>
-      <c r="BO4" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="BP4" s="12" t="n">
-        <v>101</v>
       </c>
       <c r="BQ4" s="12" t="n">
         <v>153</v>
       </c>
       <c r="BR4" s="16"/>
-      <c r="BS4" s="15" t="n">
+      <c r="BS4" s="14" t="n">
         <v>97</v>
       </c>
-      <c r="BT4" s="15" t="n">
+      <c r="BT4" s="14" t="n">
         <v>114</v>
       </c>
       <c r="BU4" s="12" t="n">
@@ -2617,13 +2617,13 @@
         <v>94</v>
       </c>
       <c r="CF4" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="CG4" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="CG4" s="13" t="s">
+      <c r="CH4" s="13" t="s">
         <v>152</v>
-      </c>
-      <c r="CH4" s="12" t="n">
-        <v>100</v>
       </c>
       <c r="CJ4" s="12" t="n">
         <v>149</v>
@@ -2643,7 +2643,7 @@
       <c r="CO4" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="CP4" s="15" t="n">
+      <c r="CP4" s="14" t="n">
         <v>94</v>
       </c>
       <c r="CQ4" s="17"/>
@@ -2767,14 +2767,14 @@
       <c r="W5" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="X5" s="13" t="s">
+      <c r="X5" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="Y5" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Y5" s="12" t="n">
+      <c r="Z5" s="12" t="n">
         <v>96</v>
-      </c>
-      <c r="Z5" s="12" t="n">
-        <v>103</v>
       </c>
       <c r="AA5" s="12" t="n">
         <v>142</v>
@@ -2785,52 +2785,52 @@
       <c r="AC5" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="AD5" s="16"/>
-      <c r="AE5" s="12" t="n">
+      <c r="AD5" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="AF5" s="15" t="n">
+      <c r="AE5" s="14" t="n">
         <v>148</v>
       </c>
-      <c r="AG5" s="13" t="s">
+      <c r="AF5" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AH5" s="13" t="s">
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="AI5" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="AI5" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="AJ5" s="14" t="s">
+      <c r="AJ5" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AK5" s="16"/>
-      <c r="AL5" s="14" t="s">
+      <c r="AL5" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM5" s="13" t="s">
         <v>202</v>
       </c>
       <c r="AN5" s="16"/>
-      <c r="AO5" s="14" t="s">
+      <c r="AO5" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP5" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="AQ5" s="14" t="s">
+      <c r="AQ5" s="15" t="s">
         <v>203</v>
       </c>
       <c r="AR5" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="AS5" s="14" t="s">
+      <c r="AS5" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AT5" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="AU5" s="14" t="s">
+      <c r="AU5" s="15" t="s">
         <v>183</v>
       </c>
       <c r="AV5" s="12" t="n">
@@ -2849,7 +2849,7 @@
       <c r="BA5" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="BB5" s="14" t="s">
+      <c r="BB5" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC5" s="12" t="n">
@@ -2884,24 +2884,24 @@
         <v>107</v>
       </c>
       <c r="BN5" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="BO5" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="BP5" s="12" t="n">
         <v>127</v>
-      </c>
-      <c r="BO5" s="12" t="n">
-        <v>132</v>
-      </c>
-      <c r="BP5" s="12" t="n">
-        <v>182</v>
       </c>
       <c r="BQ5" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="BR5" s="14" t="s">
+      <c r="BR5" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="BS5" s="15" t="n">
+      <c r="BS5" s="14" t="n">
         <v>111</v>
       </c>
-      <c r="BT5" s="15" t="n">
+      <c r="BT5" s="14" t="n">
         <v>114</v>
       </c>
       <c r="BU5" s="12" t="n">
@@ -2938,13 +2938,13 @@
         <v>110</v>
       </c>
       <c r="CF5" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="CG5" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="CG5" s="13" t="s">
+      <c r="CH5" s="13" t="s">
         <v>207</v>
-      </c>
-      <c r="CH5" s="12" t="n">
-        <v>90</v>
       </c>
       <c r="CJ5" s="12" t="n">
         <v>106</v>
@@ -2964,7 +2964,7 @@
       <c r="CO5" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="CP5" s="15" t="n">
+      <c r="CP5" s="14" t="n">
         <v>150</v>
       </c>
       <c r="CQ5" s="17"/>
@@ -3088,12 +3088,12 @@
       <c r="W6" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="12" t="n">
+      <c r="X6" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="12" t="n">
         <v>62</v>
-      </c>
-      <c r="Z6" s="12" t="n">
-        <v>80</v>
       </c>
       <c r="AA6" s="12" t="n">
         <v>80</v>
@@ -3104,38 +3104,38 @@
       <c r="AC6" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="12" t="n">
+      <c r="AD6" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="AF6" s="15" t="n">
+      <c r="AE6" s="14" t="n">
         <v>105</v>
       </c>
-      <c r="AG6" s="13" t="s">
+      <c r="AF6" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="AH6" s="13" t="s">
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI6" s="13" t="s">
         <v>222</v>
-      </c>
-      <c r="AI6" s="12" t="n">
-        <v>90</v>
       </c>
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
-      <c r="AL6" s="14" t="s">
+      <c r="AL6" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM6" s="13" t="s">
         <v>205</v>
       </c>
       <c r="AN6" s="16"/>
-      <c r="AO6" s="14" t="s">
+      <c r="AO6" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP6" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="AQ6" s="14" t="s">
+      <c r="AQ6" s="15" t="s">
         <v>223</v>
       </c>
       <c r="AR6" s="12" t="n">
@@ -3145,7 +3145,7 @@
       <c r="AT6" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="AU6" s="14" t="s">
+      <c r="AU6" s="15" t="s">
         <v>187</v>
       </c>
       <c r="AV6" s="12" t="n">
@@ -3164,7 +3164,7 @@
       <c r="BA6" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="BB6" s="14" t="s">
+      <c r="BB6" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC6" s="12" t="n">
@@ -3199,22 +3199,22 @@
         <v>107</v>
       </c>
       <c r="BN6" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="BO6" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="BP6" s="12" t="n">
         <v>124</v>
-      </c>
-      <c r="BO6" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="BP6" s="12" t="n">
-        <v>63</v>
       </c>
       <c r="BQ6" s="12" t="n">
         <v>112</v>
       </c>
       <c r="BR6" s="16"/>
-      <c r="BS6" s="15" t="n">
+      <c r="BS6" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="BT6" s="15" t="n">
+      <c r="BT6" s="14" t="n">
         <v>104</v>
       </c>
       <c r="BU6" s="12" t="n">
@@ -3251,13 +3251,13 @@
         <v>110</v>
       </c>
       <c r="CF6" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="CG6" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="CG6" s="13" t="s">
+      <c r="CH6" s="13" t="s">
         <v>228</v>
-      </c>
-      <c r="CH6" s="12" t="n">
-        <v>82</v>
       </c>
       <c r="CJ6" s="12" t="n">
         <v>80</v>
@@ -3277,7 +3277,7 @@
       <c r="CO6" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="CP6" s="15" t="n">
+      <c r="CP6" s="14" t="n">
         <v>94</v>
       </c>
       <c r="CQ6" s="17"/>
@@ -3399,14 +3399,14 @@
       <c r="W7" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="X7" s="13" t="s">
+      <c r="X7" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="Y7" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Y7" s="12" t="n">
+      <c r="Z7" s="12" t="n">
         <v>143</v>
-      </c>
-      <c r="Z7" s="12" t="n">
-        <v>246</v>
       </c>
       <c r="AA7" s="12" t="n">
         <v>198</v>
@@ -3417,52 +3417,52 @@
       <c r="AC7" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="AD7" s="16"/>
-      <c r="AE7" s="12" t="n">
+      <c r="AD7" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="AF7" s="15" t="n">
+      <c r="AE7" s="14" t="n">
         <v>142</v>
       </c>
-      <c r="AG7" s="13" t="s">
+      <c r="AF7" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="AH7" s="13" t="s">
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="AI7" s="13" t="s">
         <v>243</v>
-      </c>
-      <c r="AI7" s="12" t="n">
-        <v>106</v>
       </c>
       <c r="AJ7" s="16"/>
       <c r="AK7" s="16"/>
-      <c r="AL7" s="14" t="s">
+      <c r="AL7" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM7" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AN7" s="14" t="s">
+      <c r="AN7" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AO7" s="14" t="s">
+      <c r="AO7" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP7" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="AQ7" s="14" t="s">
+      <c r="AQ7" s="15" t="s">
         <v>136</v>
       </c>
       <c r="AR7" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="AS7" s="14" t="s">
+      <c r="AS7" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AT7" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="AU7" s="14" t="s">
+      <c r="AU7" s="15" t="s">
         <v>244</v>
       </c>
       <c r="AV7" s="12" t="n">
@@ -3481,7 +3481,7 @@
       <c r="BA7" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="BB7" s="14" t="s">
+      <c r="BB7" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC7" s="12" t="n">
@@ -3499,7 +3499,7 @@
       <c r="BG7" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="BH7" s="14" t="s">
+      <c r="BH7" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BI7" s="12" t="n">
@@ -3518,22 +3518,22 @@
         <v>176</v>
       </c>
       <c r="BN7" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="BO7" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="BP7" s="12" t="n">
         <v>158</v>
-      </c>
-      <c r="BO7" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="BP7" s="12" t="n">
-        <v>86</v>
       </c>
       <c r="BQ7" s="12" t="n">
         <v>160</v>
       </c>
       <c r="BR7" s="16"/>
-      <c r="BS7" s="15" t="n">
+      <c r="BS7" s="14" t="n">
         <v>113</v>
       </c>
-      <c r="BT7" s="15" t="n">
+      <c r="BT7" s="14" t="n">
         <v>150</v>
       </c>
       <c r="BU7" s="12" t="n">
@@ -3570,13 +3570,13 @@
         <v>138</v>
       </c>
       <c r="CF7" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="CG7" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="CG7" s="13" t="s">
+      <c r="CH7" s="13" t="s">
         <v>245</v>
-      </c>
-      <c r="CH7" s="12" t="n">
-        <v>108</v>
       </c>
       <c r="CJ7" s="12" t="n">
         <v>97</v>
@@ -3596,7 +3596,7 @@
       <c r="CO7" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="CP7" s="15" t="n">
+      <c r="CP7" s="14" t="n">
         <v>93</v>
       </c>
       <c r="CQ7" s="17"/>
@@ -3716,14 +3716,14 @@
       <c r="W8" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="X8" s="13" t="s">
+      <c r="X8" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="Y8" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Y8" s="12" t="n">
+      <c r="Z8" s="12" t="n">
         <v>139</v>
-      </c>
-      <c r="Z8" s="12" t="n">
-        <v>106</v>
       </c>
       <c r="AA8" s="12" t="n">
         <v>78</v>
@@ -3734,34 +3734,34 @@
       <c r="AC8" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="AD8" s="16"/>
-      <c r="AE8" s="12" t="n">
+      <c r="AD8" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="AF8" s="15" t="n">
+      <c r="AE8" s="14" t="n">
         <v>123</v>
       </c>
-      <c r="AG8" s="13" t="s">
+      <c r="AF8" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="12" t="n">
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="12" t="n">
         <v>95</v>
       </c>
+      <c r="AI8" s="13"/>
       <c r="AJ8" s="16"/>
       <c r="AK8" s="16"/>
-      <c r="AL8" s="14" t="s">
+      <c r="AL8" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM8" s="13" t="s">
         <v>161</v>
       </c>
       <c r="AN8" s="16"/>
-      <c r="AO8" s="14"/>
+      <c r="AO8" s="15"/>
       <c r="AP8" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="AQ8" s="14" t="s">
+      <c r="AQ8" s="15" t="s">
         <v>257</v>
       </c>
       <c r="AR8" s="12" t="n">
@@ -3771,7 +3771,7 @@
       <c r="AT8" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="AU8" s="14" t="s">
+      <c r="AU8" s="15" t="s">
         <v>258</v>
       </c>
       <c r="AV8" s="12" t="n">
@@ -3790,7 +3790,7 @@
       <c r="BA8" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="BB8" s="14" t="s">
+      <c r="BB8" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC8" s="12" t="n">
@@ -3821,22 +3821,22 @@
         <v>81</v>
       </c>
       <c r="BN8" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="BO8" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="BP8" s="12" t="n">
         <v>94</v>
-      </c>
-      <c r="BO8" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="BP8" s="12" t="n">
-        <v>52</v>
       </c>
       <c r="BQ8" s="12" t="n">
         <v>101</v>
       </c>
       <c r="BR8" s="16"/>
-      <c r="BS8" s="15" t="n">
+      <c r="BS8" s="14" t="n">
         <v>115</v>
       </c>
-      <c r="BT8" s="15" t="n">
+      <c r="BT8" s="14" t="n">
         <v>104</v>
       </c>
       <c r="BU8" s="12" t="n">
@@ -3873,13 +3873,13 @@
         <v>103</v>
       </c>
       <c r="CF8" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="CG8" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="CG8" s="13" t="s">
+      <c r="CH8" s="13" t="s">
         <v>261</v>
-      </c>
-      <c r="CH8" s="12" t="n">
-        <v>120</v>
       </c>
       <c r="CJ8" s="12" t="n">
         <v>94</v>
@@ -3899,7 +3899,7 @@
       <c r="CO8" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="CP8" s="15" t="n">
+      <c r="CP8" s="14" t="n">
         <v>131</v>
       </c>
       <c r="CQ8" s="17"/>
@@ -4021,14 +4021,14 @@
       <c r="W9" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="X9" s="13" t="s">
+      <c r="X9" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y9" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="Y9" s="12" t="n">
+      <c r="Z9" s="12" t="n">
         <v>124</v>
-      </c>
-      <c r="Z9" s="12" t="n">
-        <v>69</v>
       </c>
       <c r="AA9" s="12" t="n">
         <v>68</v>
@@ -4039,38 +4039,38 @@
       <c r="AC9" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="AD9" s="14" t="s">
+      <c r="AD9" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="AE9" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="AF9" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG9" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AE9" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="AF9" s="15" t="n">
-        <v>83</v>
-      </c>
-      <c r="AG9" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="12" t="n">
+      <c r="AH9" s="12" t="n">
         <v>98</v>
       </c>
+      <c r="AI9" s="13"/>
       <c r="AJ9" s="16"/>
       <c r="AK9" s="16"/>
-      <c r="AL9" s="14" t="s">
+      <c r="AL9" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM9" s="13" t="s">
         <v>271</v>
       </c>
       <c r="AN9" s="16"/>
-      <c r="AO9" s="14" t="s">
+      <c r="AO9" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP9" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="AQ9" s="14" t="s">
+      <c r="AQ9" s="15" t="s">
         <v>202</v>
       </c>
       <c r="AR9" s="12" t="n">
@@ -4080,7 +4080,7 @@
       <c r="AT9" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="AU9" s="14" t="s">
+      <c r="AU9" s="15" t="s">
         <v>258</v>
       </c>
       <c r="AV9" s="12" t="n">
@@ -4099,7 +4099,7 @@
       <c r="BA9" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="BB9" s="14"/>
+      <c r="BB9" s="15"/>
       <c r="BC9" s="12" t="n">
         <v>94</v>
       </c>
@@ -4128,22 +4128,22 @@
         <v>100</v>
       </c>
       <c r="BN9" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="BO9" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="BP9" s="12" t="n">
         <v>96</v>
-      </c>
-      <c r="BO9" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="BP9" s="12" t="n">
-        <v>90</v>
       </c>
       <c r="BQ9" s="12" t="n">
         <v>83</v>
       </c>
       <c r="BR9" s="16"/>
-      <c r="BS9" s="15" t="n">
+      <c r="BS9" s="14" t="n">
         <v>102</v>
       </c>
-      <c r="BT9" s="15" t="n">
+      <c r="BT9" s="14" t="n">
         <v>102</v>
       </c>
       <c r="BU9" s="12" t="n">
@@ -4180,13 +4180,13 @@
         <v>93</v>
       </c>
       <c r="CF9" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="CG9" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="CG9" s="13" t="s">
+      <c r="CH9" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="CH9" s="12" t="n">
-        <v>111</v>
       </c>
       <c r="CJ9" s="12" t="n">
         <v>94</v>
@@ -4206,7 +4206,7 @@
       <c r="CO9" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="CP9" s="15" t="n">
+      <c r="CP9" s="14" t="n">
         <v>107</v>
       </c>
       <c r="CQ9" s="17"/>
@@ -4328,12 +4328,12 @@
       <c r="W10" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="12" t="n">
+      <c r="X10" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="12" t="n">
         <v>63</v>
-      </c>
-      <c r="Z10" s="12" t="n">
-        <v>55</v>
       </c>
       <c r="AA10" s="12" t="n">
         <v>48</v>
@@ -4344,36 +4344,36 @@
       <c r="AC10" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="12" t="n">
+      <c r="AD10" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="AF10" s="15" t="n">
+      <c r="AE10" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="AG10" s="13" t="s">
+      <c r="AF10" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="AH10" s="13"/>
-      <c r="AI10" s="12" t="n">
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="12" t="n">
         <v>86</v>
       </c>
+      <c r="AI10" s="13"/>
       <c r="AJ10" s="16"/>
       <c r="AK10" s="16"/>
-      <c r="AL10" s="14" t="s">
+      <c r="AL10" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM10" s="13" t="s">
         <v>198</v>
       </c>
       <c r="AN10" s="16"/>
-      <c r="AO10" s="14" t="s">
+      <c r="AO10" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP10" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="AQ10" s="14" t="s">
+      <c r="AQ10" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AR10" s="12" t="n">
@@ -4383,7 +4383,7 @@
       <c r="AT10" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="AU10" s="14" t="s">
+      <c r="AU10" s="15" t="s">
         <v>253</v>
       </c>
       <c r="AV10" s="12" t="n">
@@ -4402,7 +4402,7 @@
       <c r="BA10" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="BB10" s="14" t="s">
+      <c r="BB10" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC10" s="12" t="n">
@@ -4433,22 +4433,22 @@
         <v>77</v>
       </c>
       <c r="BN10" s="12" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="BO10" s="12" t="n">
         <v>75</v>
       </c>
       <c r="BP10" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="BQ10" s="12" t="n">
         <v>53</v>
       </c>
       <c r="BR10" s="16"/>
-      <c r="BS10" s="15" t="n">
+      <c r="BS10" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="BT10" s="15" t="n">
+      <c r="BT10" s="14" t="n">
         <v>75</v>
       </c>
       <c r="BU10" s="12" t="n">
@@ -4485,13 +4485,13 @@
         <v>84</v>
       </c>
       <c r="CF10" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="CG10" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="CG10" s="13" t="s">
+      <c r="CH10" s="13" t="s">
         <v>151</v>
-      </c>
-      <c r="CH10" s="12" t="n">
-        <v>100</v>
       </c>
       <c r="CJ10" s="12" t="n">
         <v>83</v>
@@ -4511,7 +4511,7 @@
       <c r="CO10" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="CP10" s="15" t="n">
+      <c r="CP10" s="14" t="n">
         <v>100</v>
       </c>
       <c r="CQ10" s="17"/>
@@ -4633,12 +4633,12 @@
       <c r="W11" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="12" t="n">
+      <c r="X11" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="12" t="n">
         <v>79</v>
-      </c>
-      <c r="Z11" s="12" t="n">
-        <v>63</v>
       </c>
       <c r="AA11" s="12" t="n">
         <v>43</v>
@@ -4649,46 +4649,46 @@
       <c r="AC11" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="12" t="n">
+      <c r="AD11" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="AF11" s="15" t="n">
+      <c r="AE11" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="AG11" s="13" t="s">
+      <c r="AF11" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="12" t="n">
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="12" t="n">
         <v>83</v>
       </c>
+      <c r="AI11" s="13"/>
       <c r="AJ11" s="16"/>
       <c r="AK11" s="16"/>
-      <c r="AL11" s="14" t="s">
+      <c r="AL11" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM11" s="13" t="s">
         <v>186</v>
       </c>
       <c r="AN11" s="16"/>
-      <c r="AO11" s="14"/>
+      <c r="AO11" s="15"/>
       <c r="AP11" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="AQ11" s="14" t="s">
+      <c r="AQ11" s="15" t="s">
         <v>214</v>
       </c>
       <c r="AR11" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="AS11" s="14" t="s">
+      <c r="AS11" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AT11" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="AU11" s="14" t="s">
+      <c r="AU11" s="15" t="s">
         <v>266</v>
       </c>
       <c r="AV11" s="12" t="n">
@@ -4707,7 +4707,7 @@
       <c r="BA11" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="BB11" s="14" t="s">
+      <c r="BB11" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC11" s="12" t="n">
@@ -4738,22 +4738,22 @@
         <v>76</v>
       </c>
       <c r="BN11" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="BO11" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="BP11" s="12" t="n">
         <v>73</v>
-      </c>
-      <c r="BO11" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="BP11" s="12" t="n">
-        <v>105</v>
       </c>
       <c r="BQ11" s="12" t="n">
         <v>72</v>
       </c>
       <c r="BR11" s="16"/>
-      <c r="BS11" s="15" t="n">
+      <c r="BS11" s="14" t="n">
         <v>106</v>
       </c>
-      <c r="BT11" s="15" t="n">
+      <c r="BT11" s="14" t="n">
         <v>80</v>
       </c>
       <c r="BU11" s="12" t="n">
@@ -4787,13 +4787,13 @@
         <v>86</v>
       </c>
       <c r="CF11" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="CG11" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="CG11" s="13" t="s">
+      <c r="CH11" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="CH11" s="12" t="n">
-        <v>91</v>
       </c>
       <c r="CJ11" s="12" t="n">
         <v>91</v>
@@ -4813,7 +4813,7 @@
       <c r="CO11" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="CP11" s="15" t="n">
+      <c r="CP11" s="14" t="n">
         <v>80</v>
       </c>
       <c r="CQ11" s="17"/>
@@ -4933,12 +4933,12 @@
       <c r="W12" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="12" t="n">
+      <c r="X12" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="12" t="n">
         <v>59</v>
-      </c>
-      <c r="Z12" s="12" t="n">
-        <v>79</v>
       </c>
       <c r="AA12" s="12" t="n">
         <v>52</v>
@@ -4949,34 +4949,34 @@
       <c r="AC12" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="AD12" s="16"/>
-      <c r="AE12" s="12" t="n">
+      <c r="AD12" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="AF12" s="15" t="n">
+      <c r="AE12" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="AG12" s="13" t="s">
+      <c r="AF12" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="12" t="n">
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="12" t="n">
         <v>84</v>
       </c>
+      <c r="AI12" s="13"/>
       <c r="AJ12" s="16"/>
       <c r="AK12" s="16"/>
-      <c r="AL12" s="14"/>
+      <c r="AL12" s="15"/>
       <c r="AM12" s="13" t="s">
         <v>245</v>
       </c>
       <c r="AN12" s="16"/>
-      <c r="AO12" s="14" t="s">
+      <c r="AO12" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP12" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="AQ12" s="14" t="s">
+      <c r="AQ12" s="15" t="s">
         <v>213</v>
       </c>
       <c r="AR12" s="12" t="n">
@@ -4986,7 +4986,7 @@
       <c r="AT12" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="AU12" s="14" t="s">
+      <c r="AU12" s="15" t="s">
         <v>285</v>
       </c>
       <c r="AV12" s="12" t="n">
@@ -5005,7 +5005,7 @@
       <c r="BA12" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="BB12" s="14"/>
+      <c r="BB12" s="15"/>
       <c r="BC12" s="12" t="n">
         <v>103</v>
       </c>
@@ -5037,19 +5037,19 @@
         <v>78</v>
       </c>
       <c r="BO12" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="BP12" s="12" t="n">
         <v>78</v>
-      </c>
-      <c r="BP12" s="12" t="n">
-        <v>126</v>
       </c>
       <c r="BQ12" s="12" t="n">
         <v>61</v>
       </c>
       <c r="BR12" s="16"/>
-      <c r="BS12" s="15" t="n">
+      <c r="BS12" s="14" t="n">
         <v>103</v>
       </c>
-      <c r="BT12" s="15" t="n">
+      <c r="BT12" s="14" t="n">
         <v>63</v>
       </c>
       <c r="BU12" s="12" t="n">
@@ -5086,13 +5086,13 @@
         <v>90</v>
       </c>
       <c r="CF12" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="CG12" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="CG12" s="13" t="s">
+      <c r="CH12" s="13" t="s">
         <v>296</v>
-      </c>
-      <c r="CH12" s="12" t="n">
-        <v>93</v>
       </c>
       <c r="CJ12" s="12" t="n">
         <v>86</v>
@@ -5112,7 +5112,7 @@
       <c r="CO12" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="CP12" s="15" t="n">
+      <c r="CP12" s="14" t="n">
         <v>126</v>
       </c>
       <c r="CQ12" s="17"/>
@@ -5234,12 +5234,12 @@
       <c r="W13" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="12" t="n">
+      <c r="X13" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="12" t="n">
         <v>30</v>
-      </c>
-      <c r="Z13" s="12" t="n">
-        <v>25</v>
       </c>
       <c r="AA13" s="12" t="n">
         <v>30</v>
@@ -5250,38 +5250,38 @@
       <c r="AC13" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="AD13" s="14" t="s">
+      <c r="AD13" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE13" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF13" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="AG13" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="AE13" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG13" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="12" t="n">
+      <c r="AH13" s="12" t="n">
         <v>79</v>
       </c>
+      <c r="AI13" s="13"/>
       <c r="AJ13" s="16"/>
       <c r="AK13" s="16"/>
-      <c r="AL13" s="14" t="s">
+      <c r="AL13" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AM13" s="13" t="s">
         <v>177</v>
       </c>
       <c r="AN13" s="16"/>
-      <c r="AO13" s="14" t="s">
+      <c r="AO13" s="15" t="s">
         <v>119</v>
       </c>
       <c r="AP13" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="AQ13" s="14" t="s">
+      <c r="AQ13" s="15" t="s">
         <v>293</v>
       </c>
       <c r="AR13" s="12" t="n">
@@ -5291,7 +5291,7 @@
       <c r="AT13" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="AU13" s="14" t="s">
+      <c r="AU13" s="15" t="s">
         <v>180</v>
       </c>
       <c r="AV13" s="12" t="n">
@@ -5310,7 +5310,7 @@
       <c r="BA13" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="BB13" s="14" t="s">
+      <c r="BB13" s="15" t="s">
         <v>119</v>
       </c>
       <c r="BC13" s="12" t="n">
@@ -5341,22 +5341,22 @@
         <v>100</v>
       </c>
       <c r="BN13" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="BO13" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="BP13" s="12" t="n">
         <v>70</v>
-      </c>
-      <c r="BO13" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="BP13" s="12" t="n">
-        <v>95</v>
       </c>
       <c r="BQ13" s="12" t="n">
         <v>57</v>
       </c>
       <c r="BR13" s="16"/>
-      <c r="BS13" s="15" t="n">
+      <c r="BS13" s="14" t="n">
         <v>81</v>
       </c>
-      <c r="BT13" s="15" t="n">
+      <c r="BT13" s="14" t="n">
         <v>57</v>
       </c>
       <c r="BU13" s="12" t="n">
@@ -5390,13 +5390,13 @@
         <v>76</v>
       </c>
       <c r="CF13" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="CG13" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="CG13" s="13" t="s">
+      <c r="CH13" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="CH13" s="12" t="n">
-        <v>88</v>
       </c>
       <c r="CJ13" s="12" t="n">
         <v>92</v>
@@ -5416,7 +5416,7 @@
       <c r="CO13" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="CP13" s="15" t="n">
+      <c r="CP13" s="14" t="n">
         <v>88</v>
       </c>
       <c r="CQ13" s="17"/>
@@ -5494,18 +5494,18 @@
       <c r="U14" s="21"/>
       <c r="V14" s="22"/>
       <c r="W14" s="22"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="21"/>
       <c r="Z14" s="22"/>
       <c r="AA14" s="22"/>
       <c r="AB14" s="21"/>
       <c r="AC14" s="21"/>
-      <c r="AD14" s="16"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="17"/>
-      <c r="AG14" s="23"/>
-      <c r="AH14" s="23"/>
-      <c r="AI14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="22"/>
+      <c r="AI14" s="23"/>
       <c r="AJ14" s="16"/>
       <c r="AK14" s="16"/>
       <c r="AL14" s="16"/>
@@ -5555,8 +5555,8 @@
       <c r="CD14" s="22"/>
       <c r="CE14" s="22"/>
       <c r="CF14" s="22"/>
-      <c r="CG14" s="21"/>
-      <c r="CH14" s="22"/>
+      <c r="CG14" s="22"/>
+      <c r="CH14" s="21"/>
       <c r="CI14" s="22"/>
       <c r="CJ14" s="22"/>
       <c r="CK14" s="22"/>
@@ -5597,14 +5597,14 @@
       <c r="S15" s="20"/>
       <c r="T15" s="20"/>
       <c r="U15" s="20"/>
-      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20"/>
-      <c r="AD15" s="16"/>
-      <c r="AF15" s="17"/>
-      <c r="AG15" s="25"/>
-      <c r="AH15" s="25"/>
-      <c r="AI15" s="26"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="25"/>
       <c r="AJ15" s="16"/>
       <c r="AK15" s="16"/>
       <c r="AL15" s="16"/>
@@ -5629,7 +5629,7 @@
       <c r="BW15" s="20"/>
       <c r="BX15" s="20"/>
       <c r="BY15" s="20"/>
-      <c r="CG15" s="20"/>
+      <c r="CH15" s="20"/>
       <c r="CO15" s="27"/>
       <c r="CP15" s="17"/>
       <c r="CQ15" s="17"/>
@@ -5653,14 +5653,14 @@
       <c r="S16" s="20"/>
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
-      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20"/>
-      <c r="AD16" s="16"/>
-      <c r="AF16" s="17"/>
-      <c r="AG16" s="25"/>
-      <c r="AH16" s="25"/>
-      <c r="AI16" s="26"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="26"/>
+      <c r="AI16" s="25"/>
       <c r="AJ16" s="16"/>
       <c r="AK16" s="16"/>
       <c r="AL16" s="16"/>
@@ -5685,7 +5685,7 @@
       <c r="BW16" s="20"/>
       <c r="BX16" s="20"/>
       <c r="BY16" s="20"/>
-      <c r="CG16" s="20"/>
+      <c r="CH16" s="20"/>
       <c r="CO16" s="27"/>
       <c r="CP16" s="17"/>
       <c r="CQ16" s="17"/>
@@ -5709,14 +5709,14 @@
       <c r="S17" s="20"/>
       <c r="T17" s="20"/>
       <c r="U17" s="20"/>
-      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20"/>
-      <c r="AD17" s="16"/>
-      <c r="AF17" s="17"/>
-      <c r="AG17" s="25"/>
-      <c r="AH17" s="25"/>
-      <c r="AI17" s="26"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="26"/>
+      <c r="AI17" s="25"/>
       <c r="AJ17" s="16"/>
       <c r="AK17" s="16"/>
       <c r="AL17" s="16"/>
@@ -5741,7 +5741,7 @@
       <c r="BW17" s="20"/>
       <c r="BX17" s="20"/>
       <c r="BY17" s="20"/>
-      <c r="CG17" s="20"/>
+      <c r="CH17" s="20"/>
       <c r="CO17" s="27"/>
       <c r="CP17" s="17"/>
       <c r="CQ17" s="17"/>
@@ -5765,14 +5765,14 @@
       <c r="S18" s="20"/>
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
-      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20"/>
-      <c r="AD18" s="16"/>
-      <c r="AF18" s="17"/>
-      <c r="AG18" s="25"/>
-      <c r="AH18" s="25"/>
-      <c r="AI18" s="26"/>
+      <c r="AE18" s="17"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="26"/>
+      <c r="AI18" s="25"/>
       <c r="AJ18" s="16"/>
       <c r="AK18" s="16"/>
       <c r="AL18" s="16"/>
@@ -5797,7 +5797,7 @@
       <c r="BW18" s="20"/>
       <c r="BX18" s="20"/>
       <c r="BY18" s="20"/>
-      <c r="CG18" s="20"/>
+      <c r="CH18" s="20"/>
       <c r="CO18" s="27"/>
       <c r="CP18" s="17"/>
       <c r="CQ18" s="17"/>
@@ -5828,14 +5828,14 @@
       <c r="S19" s="20"/>
       <c r="T19" s="20"/>
       <c r="U19" s="20"/>
-      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20"/>
-      <c r="AD19" s="16"/>
-      <c r="AF19" s="17"/>
-      <c r="AG19" s="25"/>
-      <c r="AH19" s="25"/>
-      <c r="AI19" s="26"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="26"/>
+      <c r="AI19" s="25"/>
       <c r="AJ19" s="16"/>
       <c r="AK19" s="16"/>
       <c r="AL19" s="16"/>
@@ -5860,7 +5860,7 @@
       <c r="BW19" s="20"/>
       <c r="BX19" s="20"/>
       <c r="BY19" s="20"/>
-      <c r="CG19" s="20"/>
+      <c r="CH19" s="20"/>
       <c r="CO19" s="27"/>
       <c r="CP19" s="17"/>
       <c r="CQ19" s="17"/>
@@ -5891,14 +5891,14 @@
       <c r="S20" s="20"/>
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
-      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20"/>
-      <c r="AD20" s="16"/>
-      <c r="AF20" s="17"/>
-      <c r="AG20" s="25"/>
-      <c r="AH20" s="25"/>
-      <c r="AI20" s="26"/>
+      <c r="AE20" s="17"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="26"/>
+      <c r="AI20" s="25"/>
       <c r="AJ20" s="16"/>
       <c r="AK20" s="16"/>
       <c r="AL20" s="16"/>
@@ -5923,7 +5923,7 @@
       <c r="BW20" s="20"/>
       <c r="BX20" s="20"/>
       <c r="BY20" s="20"/>
-      <c r="CG20" s="20"/>
+      <c r="CH20" s="20"/>
       <c r="CO20" s="27"/>
       <c r="CP20" s="17"/>
       <c r="CQ20" s="17"/>
@@ -5954,14 +5954,14 @@
       <c r="S21" s="20"/>
       <c r="T21" s="20"/>
       <c r="U21" s="20"/>
-      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
       <c r="AB21" s="20"/>
       <c r="AC21" s="20"/>
-      <c r="AD21" s="16"/>
-      <c r="AF21" s="17"/>
-      <c r="AG21" s="25"/>
-      <c r="AH21" s="25"/>
-      <c r="AI21" s="26"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="26"/>
+      <c r="AI21" s="25"/>
       <c r="AJ21" s="16"/>
       <c r="AK21" s="16"/>
       <c r="AL21" s="16"/>
@@ -5986,7 +5986,7 @@
       <c r="BW21" s="20"/>
       <c r="BX21" s="20"/>
       <c r="BY21" s="20"/>
-      <c r="CG21" s="20"/>
+      <c r="CH21" s="20"/>
       <c r="CO21" s="27"/>
       <c r="CP21" s="17"/>
       <c r="CQ21" s="17"/>
@@ -6017,14 +6017,14 @@
       <c r="S22" s="20"/>
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
-      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
       <c r="AB22" s="20"/>
       <c r="AC22" s="20"/>
-      <c r="AD22" s="16"/>
-      <c r="AF22" s="17"/>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="25"/>
-      <c r="AI22" s="26"/>
+      <c r="AE22" s="17"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="26"/>
+      <c r="AI22" s="25"/>
       <c r="AJ22" s="16"/>
       <c r="AK22" s="16"/>
       <c r="AL22" s="16"/>
@@ -6049,7 +6049,7 @@
       <c r="BW22" s="20"/>
       <c r="BX22" s="20"/>
       <c r="BY22" s="20"/>
-      <c r="CG22" s="20"/>
+      <c r="CH22" s="20"/>
       <c r="CO22" s="27"/>
       <c r="CP22" s="17"/>
       <c r="CQ22" s="17"/>
@@ -6080,14 +6080,14 @@
       <c r="S23" s="20"/>
       <c r="T23" s="20"/>
       <c r="U23" s="20"/>
-      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
       <c r="AB23" s="20"/>
       <c r="AC23" s="20"/>
-      <c r="AD23" s="16"/>
-      <c r="AF23" s="17"/>
-      <c r="AG23" s="25"/>
-      <c r="AH23" s="25"/>
-      <c r="AI23" s="26"/>
+      <c r="AE23" s="17"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="26"/>
+      <c r="AI23" s="25"/>
       <c r="AJ23" s="16"/>
       <c r="AK23" s="16"/>
       <c r="AL23" s="16"/>
@@ -6112,7 +6112,7 @@
       <c r="BW23" s="20"/>
       <c r="BX23" s="20"/>
       <c r="BY23" s="20"/>
-      <c r="CG23" s="20"/>
+      <c r="CH23" s="20"/>
       <c r="CO23" s="27"/>
       <c r="CP23" s="17"/>
       <c r="CQ23" s="17"/>
@@ -6143,14 +6143,14 @@
       <c r="S24" s="20"/>
       <c r="T24" s="20"/>
       <c r="U24" s="20"/>
-      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
       <c r="AB24" s="20"/>
       <c r="AC24" s="20"/>
-      <c r="AD24" s="16"/>
-      <c r="AF24" s="17"/>
-      <c r="AG24" s="25"/>
-      <c r="AH24" s="25"/>
-      <c r="AI24" s="26"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="16"/>
+      <c r="AH24" s="26"/>
+      <c r="AI24" s="25"/>
       <c r="AJ24" s="16"/>
       <c r="AK24" s="16"/>
       <c r="AL24" s="16"/>
@@ -6175,7 +6175,7 @@
       <c r="BW24" s="20"/>
       <c r="BX24" s="20"/>
       <c r="BY24" s="20"/>
-      <c r="CG24" s="20"/>
+      <c r="CH24" s="20"/>
       <c r="CO24" s="27"/>
       <c r="CP24" s="17"/>
       <c r="CQ24" s="17"/>
@@ -6206,14 +6206,14 @@
       <c r="S25" s="20"/>
       <c r="T25" s="20"/>
       <c r="U25" s="20"/>
-      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
       <c r="AB25" s="20"/>
       <c r="AC25" s="20"/>
-      <c r="AD25" s="16"/>
-      <c r="AF25" s="17"/>
-      <c r="AG25" s="25"/>
-      <c r="AH25" s="25"/>
-      <c r="AI25" s="26"/>
+      <c r="AE25" s="17"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="26"/>
+      <c r="AI25" s="25"/>
       <c r="AJ25" s="16"/>
       <c r="AK25" s="16"/>
       <c r="AL25" s="16"/>
@@ -6238,7 +6238,7 @@
       <c r="BW25" s="20"/>
       <c r="BX25" s="20"/>
       <c r="BY25" s="20"/>
-      <c r="CG25" s="20"/>
+      <c r="CH25" s="20"/>
       <c r="CO25" s="27"/>
       <c r="CP25" s="17"/>
       <c r="CQ25" s="17"/>
@@ -6269,14 +6269,14 @@
       <c r="S26" s="20"/>
       <c r="T26" s="20"/>
       <c r="U26" s="20"/>
-      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
       <c r="AB26" s="20"/>
       <c r="AC26" s="20"/>
-      <c r="AD26" s="16"/>
-      <c r="AF26" s="17"/>
-      <c r="AG26" s="25"/>
-      <c r="AH26" s="25"/>
-      <c r="AI26" s="26"/>
+      <c r="AE26" s="17"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="26"/>
+      <c r="AI26" s="25"/>
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="16"/>
@@ -6301,7 +6301,7 @@
       <c r="BW26" s="20"/>
       <c r="BX26" s="20"/>
       <c r="BY26" s="20"/>
-      <c r="CG26" s="20"/>
+      <c r="CH26" s="20"/>
       <c r="CO26" s="27"/>
       <c r="CP26" s="17"/>
       <c r="CQ26" s="17"/>
@@ -6332,14 +6332,14 @@
       <c r="S27" s="20"/>
       <c r="T27" s="20"/>
       <c r="U27" s="20"/>
-      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
       <c r="AB27" s="20"/>
       <c r="AC27" s="20"/>
-      <c r="AD27" s="16"/>
-      <c r="AF27" s="17"/>
-      <c r="AG27" s="25"/>
-      <c r="AH27" s="25"/>
-      <c r="AI27" s="26"/>
+      <c r="AE27" s="17"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="26"/>
+      <c r="AI27" s="25"/>
       <c r="AJ27" s="16"/>
       <c r="AK27" s="16"/>
       <c r="AL27" s="16"/>
@@ -6364,7 +6364,7 @@
       <c r="BW27" s="20"/>
       <c r="BX27" s="20"/>
       <c r="BY27" s="20"/>
-      <c r="CG27" s="20"/>
+      <c r="CH27" s="20"/>
       <c r="CO27" s="27"/>
       <c r="CP27" s="17"/>
       <c r="CQ27" s="17"/>
@@ -6394,14 +6394,14 @@
       <c r="S28" s="20"/>
       <c r="T28" s="20"/>
       <c r="U28" s="20"/>
-      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
       <c r="AB28" s="20"/>
       <c r="AC28" s="20"/>
-      <c r="AD28" s="16"/>
-      <c r="AF28" s="17"/>
-      <c r="AG28" s="25"/>
-      <c r="AH28" s="25"/>
-      <c r="AI28" s="26"/>
+      <c r="AE28" s="17"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="26"/>
+      <c r="AI28" s="25"/>
       <c r="AJ28" s="16"/>
       <c r="AK28" s="16"/>
       <c r="AL28" s="16"/>
@@ -6426,7 +6426,7 @@
       <c r="BW28" s="20"/>
       <c r="BX28" s="20"/>
       <c r="BY28" s="20"/>
-      <c r="CG28" s="20"/>
+      <c r="CH28" s="20"/>
       <c r="CO28" s="27"/>
       <c r="CP28" s="17"/>
       <c r="CQ28" s="17"/>
@@ -6456,14 +6456,14 @@
       <c r="S29" s="20"/>
       <c r="T29" s="20"/>
       <c r="U29" s="20"/>
-      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
       <c r="AB29" s="20"/>
       <c r="AC29" s="20"/>
-      <c r="AD29" s="16"/>
-      <c r="AF29" s="17"/>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="25"/>
-      <c r="AI29" s="26"/>
+      <c r="AE29" s="17"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="26"/>
+      <c r="AI29" s="25"/>
       <c r="AJ29" s="16"/>
       <c r="AK29" s="16"/>
       <c r="AL29" s="16"/>
@@ -6488,7 +6488,7 @@
       <c r="BW29" s="20"/>
       <c r="BX29" s="20"/>
       <c r="BY29" s="20"/>
-      <c r="CG29" s="20"/>
+      <c r="CH29" s="20"/>
       <c r="CO29" s="27"/>
       <c r="CP29" s="17"/>
       <c r="CQ29" s="17"/>
@@ -6518,14 +6518,14 @@
       <c r="S30" s="20"/>
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
-      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
       <c r="AB30" s="20"/>
       <c r="AC30" s="20"/>
-      <c r="AD30" s="16"/>
-      <c r="AF30" s="17"/>
-      <c r="AG30" s="25"/>
-      <c r="AH30" s="25"/>
-      <c r="AI30" s="26"/>
+      <c r="AE30" s="17"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="16"/>
+      <c r="AH30" s="26"/>
+      <c r="AI30" s="25"/>
       <c r="AJ30" s="16"/>
       <c r="AK30" s="16"/>
       <c r="AL30" s="16"/>
@@ -6550,7 +6550,7 @@
       <c r="BW30" s="20"/>
       <c r="BX30" s="20"/>
       <c r="BY30" s="20"/>
-      <c r="CG30" s="20"/>
+      <c r="CH30" s="20"/>
       <c r="CO30" s="27"/>
       <c r="CP30" s="17"/>
       <c r="CQ30" s="17"/>
@@ -6572,14 +6572,14 @@
       <c r="S31" s="20"/>
       <c r="T31" s="20"/>
       <c r="U31" s="20"/>
-      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
       <c r="AB31" s="20"/>
       <c r="AC31" s="20"/>
-      <c r="AD31" s="16"/>
-      <c r="AF31" s="17"/>
-      <c r="AG31" s="25"/>
-      <c r="AH31" s="25"/>
-      <c r="AI31" s="26"/>
+      <c r="AE31" s="17"/>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="16"/>
+      <c r="AH31" s="26"/>
+      <c r="AI31" s="25"/>
       <c r="AJ31" s="16"/>
       <c r="AK31" s="16"/>
       <c r="AL31" s="16"/>
@@ -6604,7 +6604,7 @@
       <c r="BW31" s="20"/>
       <c r="BX31" s="20"/>
       <c r="BY31" s="20"/>
-      <c r="CG31" s="20"/>
+      <c r="CH31" s="20"/>
       <c r="CO31" s="27"/>
       <c r="CP31" s="17"/>
       <c r="CQ31" s="17"/>
@@ -6626,14 +6626,14 @@
       <c r="S32" s="20"/>
       <c r="T32" s="20"/>
       <c r="U32" s="20"/>
-      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
       <c r="AB32" s="20"/>
       <c r="AC32" s="20"/>
-      <c r="AD32" s="16"/>
-      <c r="AF32" s="17"/>
-      <c r="AG32" s="25"/>
-      <c r="AH32" s="25"/>
-      <c r="AI32" s="26"/>
+      <c r="AE32" s="17"/>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="16"/>
+      <c r="AH32" s="26"/>
+      <c r="AI32" s="25"/>
       <c r="AJ32" s="16"/>
       <c r="AK32" s="16"/>
       <c r="AL32" s="16"/>
@@ -6658,7 +6658,7 @@
       <c r="BW32" s="20"/>
       <c r="BX32" s="20"/>
       <c r="BY32" s="20"/>
-      <c r="CG32" s="20"/>
+      <c r="CH32" s="20"/>
       <c r="CO32" s="27"/>
       <c r="CP32" s="17"/>
       <c r="CQ32" s="17"/>
@@ -6680,14 +6680,14 @@
       <c r="S33" s="20"/>
       <c r="T33" s="20"/>
       <c r="U33" s="20"/>
-      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
       <c r="AB33" s="20"/>
       <c r="AC33" s="20"/>
-      <c r="AD33" s="16"/>
-      <c r="AF33" s="17"/>
-      <c r="AG33" s="25"/>
-      <c r="AH33" s="25"/>
-      <c r="AI33" s="26"/>
+      <c r="AE33" s="17"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="16"/>
+      <c r="AH33" s="26"/>
+      <c r="AI33" s="25"/>
       <c r="AJ33" s="16"/>
       <c r="AK33" s="16"/>
       <c r="AL33" s="16"/>
@@ -6712,7 +6712,7 @@
       <c r="BW33" s="20"/>
       <c r="BX33" s="20"/>
       <c r="BY33" s="20"/>
-      <c r="CG33" s="20"/>
+      <c r="CH33" s="20"/>
       <c r="CO33" s="27"/>
       <c r="CP33" s="17"/>
       <c r="CQ33" s="17"/>
@@ -6734,14 +6734,14 @@
       <c r="S34" s="20"/>
       <c r="T34" s="20"/>
       <c r="U34" s="20"/>
-      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
       <c r="AB34" s="20"/>
       <c r="AC34" s="20"/>
-      <c r="AD34" s="16"/>
-      <c r="AF34" s="17"/>
-      <c r="AG34" s="25"/>
-      <c r="AH34" s="25"/>
-      <c r="AI34" s="26"/>
+      <c r="AE34" s="17"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="26"/>
+      <c r="AI34" s="25"/>
       <c r="AJ34" s="16"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
@@ -6766,7 +6766,7 @@
       <c r="BW34" s="20"/>
       <c r="BX34" s="20"/>
       <c r="BY34" s="20"/>
-      <c r="CG34" s="20"/>
+      <c r="CH34" s="20"/>
       <c r="CO34" s="27"/>
       <c r="CP34" s="17"/>
       <c r="CQ34" s="17"/>
@@ -6788,14 +6788,14 @@
       <c r="S35" s="20"/>
       <c r="T35" s="20"/>
       <c r="U35" s="20"/>
-      <c r="X35" s="20"/>
+      <c r="Y35" s="20"/>
       <c r="AB35" s="20"/>
       <c r="AC35" s="20"/>
-      <c r="AD35" s="16"/>
-      <c r="AF35" s="17"/>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="25"/>
-      <c r="AI35" s="26"/>
+      <c r="AE35" s="17"/>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="26"/>
+      <c r="AI35" s="25"/>
       <c r="AJ35" s="16"/>
       <c r="AK35" s="16"/>
       <c r="AL35" s="16"/>
@@ -6820,7 +6820,7 @@
       <c r="BW35" s="20"/>
       <c r="BX35" s="20"/>
       <c r="BY35" s="20"/>
-      <c r="CG35" s="20"/>
+      <c r="CH35" s="20"/>
       <c r="CO35" s="27"/>
       <c r="CP35" s="17"/>
       <c r="CQ35" s="17"/>
@@ -6842,14 +6842,14 @@
       <c r="S36" s="20"/>
       <c r="T36" s="20"/>
       <c r="U36" s="20"/>
-      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
       <c r="AB36" s="20"/>
       <c r="AC36" s="20"/>
-      <c r="AD36" s="16"/>
-      <c r="AF36" s="17"/>
-      <c r="AG36" s="25"/>
-      <c r="AH36" s="25"/>
-      <c r="AI36" s="26"/>
+      <c r="AE36" s="17"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="26"/>
+      <c r="AI36" s="25"/>
       <c r="AJ36" s="16"/>
       <c r="AK36" s="16"/>
       <c r="AL36" s="16"/>
@@ -6874,7 +6874,7 @@
       <c r="BW36" s="20"/>
       <c r="BX36" s="20"/>
       <c r="BY36" s="20"/>
-      <c r="CG36" s="20"/>
+      <c r="CH36" s="20"/>
       <c r="CO36" s="27"/>
       <c r="CP36" s="17"/>
       <c r="CQ36" s="17"/>
@@ -6896,14 +6896,14 @@
       <c r="S37" s="20"/>
       <c r="T37" s="20"/>
       <c r="U37" s="20"/>
-      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
       <c r="AB37" s="20"/>
       <c r="AC37" s="20"/>
-      <c r="AD37" s="16"/>
-      <c r="AF37" s="17"/>
-      <c r="AG37" s="25"/>
-      <c r="AH37" s="25"/>
-      <c r="AI37" s="26"/>
+      <c r="AE37" s="17"/>
+      <c r="AF37" s="25"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="26"/>
+      <c r="AI37" s="25"/>
       <c r="AJ37" s="16"/>
       <c r="AK37" s="16"/>
       <c r="AL37" s="16"/>
@@ -6928,7 +6928,7 @@
       <c r="BW37" s="20"/>
       <c r="BX37" s="20"/>
       <c r="BY37" s="20"/>
-      <c r="CG37" s="20"/>
+      <c r="CH37" s="20"/>
       <c r="CO37" s="27"/>
       <c r="CP37" s="17"/>
       <c r="CQ37" s="17"/>
@@ -6950,14 +6950,14 @@
       <c r="S38" s="20"/>
       <c r="T38" s="20"/>
       <c r="U38" s="20"/>
-      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
       <c r="AB38" s="20"/>
       <c r="AC38" s="20"/>
-      <c r="AD38" s="16"/>
-      <c r="AF38" s="17"/>
-      <c r="AG38" s="25"/>
-      <c r="AH38" s="25"/>
-      <c r="AI38" s="26"/>
+      <c r="AE38" s="17"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="16"/>
+      <c r="AH38" s="26"/>
+      <c r="AI38" s="25"/>
       <c r="AJ38" s="16"/>
       <c r="AK38" s="16"/>
       <c r="AL38" s="16"/>
@@ -6982,7 +6982,7 @@
       <c r="BW38" s="20"/>
       <c r="BX38" s="20"/>
       <c r="BY38" s="20"/>
-      <c r="CG38" s="20"/>
+      <c r="CH38" s="20"/>
       <c r="CO38" s="27"/>
       <c r="CP38" s="17"/>
       <c r="CQ38" s="17"/>
@@ -7004,14 +7004,14 @@
       <c r="S39" s="20"/>
       <c r="T39" s="20"/>
       <c r="U39" s="20"/>
-      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
       <c r="AB39" s="20"/>
       <c r="AC39" s="20"/>
-      <c r="AD39" s="16"/>
-      <c r="AF39" s="17"/>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="25"/>
-      <c r="AI39" s="26"/>
+      <c r="AE39" s="17"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="16"/>
+      <c r="AH39" s="26"/>
+      <c r="AI39" s="25"/>
       <c r="AJ39" s="16"/>
       <c r="AK39" s="16"/>
       <c r="AL39" s="16"/>
@@ -7036,7 +7036,7 @@
       <c r="BW39" s="20"/>
       <c r="BX39" s="20"/>
       <c r="BY39" s="20"/>
-      <c r="CG39" s="20"/>
+      <c r="CH39" s="20"/>
       <c r="CO39" s="27"/>
       <c r="CP39" s="17"/>
       <c r="CQ39" s="17"/>
@@ -7058,14 +7058,14 @@
       <c r="S40" s="20"/>
       <c r="T40" s="20"/>
       <c r="U40" s="20"/>
-      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
       <c r="AB40" s="20"/>
       <c r="AC40" s="20"/>
-      <c r="AD40" s="16"/>
-      <c r="AF40" s="17"/>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="25"/>
-      <c r="AI40" s="26"/>
+      <c r="AE40" s="17"/>
+      <c r="AF40" s="25"/>
+      <c r="AG40" s="16"/>
+      <c r="AH40" s="26"/>
+      <c r="AI40" s="25"/>
       <c r="AJ40" s="16"/>
       <c r="AK40" s="16"/>
       <c r="AL40" s="16"/>
@@ -7090,7 +7090,7 @@
       <c r="BW40" s="20"/>
       <c r="BX40" s="20"/>
       <c r="BY40" s="20"/>
-      <c r="CG40" s="20"/>
+      <c r="CH40" s="20"/>
       <c r="CO40" s="27"/>
       <c r="CP40" s="17"/>
       <c r="CQ40" s="17"/>
@@ -7112,14 +7112,14 @@
       <c r="S41" s="20"/>
       <c r="T41" s="20"/>
       <c r="U41" s="20"/>
-      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
       <c r="AB41" s="20"/>
       <c r="AC41" s="20"/>
-      <c r="AD41" s="16"/>
-      <c r="AF41" s="17"/>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="25"/>
-      <c r="AI41" s="26"/>
+      <c r="AE41" s="17"/>
+      <c r="AF41" s="25"/>
+      <c r="AG41" s="16"/>
+      <c r="AH41" s="26"/>
+      <c r="AI41" s="25"/>
       <c r="AJ41" s="16"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
@@ -7144,7 +7144,7 @@
       <c r="BW41" s="20"/>
       <c r="BX41" s="20"/>
       <c r="BY41" s="20"/>
-      <c r="CG41" s="20"/>
+      <c r="CH41" s="20"/>
       <c r="CO41" s="27"/>
       <c r="CP41" s="17"/>
       <c r="CQ41" s="17"/>
@@ -7166,14 +7166,14 @@
       <c r="S42" s="20"/>
       <c r="T42" s="20"/>
       <c r="U42" s="20"/>
-      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
       <c r="AB42" s="20"/>
       <c r="AC42" s="20"/>
-      <c r="AD42" s="16"/>
-      <c r="AF42" s="17"/>
-      <c r="AG42" s="25"/>
-      <c r="AH42" s="25"/>
-      <c r="AI42" s="26"/>
+      <c r="AE42" s="17"/>
+      <c r="AF42" s="25"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="26"/>
+      <c r="AI42" s="25"/>
       <c r="AJ42" s="16"/>
       <c r="AK42" s="16"/>
       <c r="AL42" s="16"/>
@@ -7198,7 +7198,7 @@
       <c r="BW42" s="20"/>
       <c r="BX42" s="20"/>
       <c r="BY42" s="20"/>
-      <c r="CG42" s="20"/>
+      <c r="CH42" s="20"/>
       <c r="CO42" s="27"/>
       <c r="CP42" s="17"/>
       <c r="CQ42" s="17"/>
@@ -7220,14 +7220,14 @@
       <c r="S43" s="20"/>
       <c r="T43" s="20"/>
       <c r="U43" s="20"/>
-      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
       <c r="AB43" s="20"/>
       <c r="AC43" s="20"/>
-      <c r="AD43" s="16"/>
-      <c r="AF43" s="17"/>
-      <c r="AG43" s="25"/>
-      <c r="AH43" s="25"/>
-      <c r="AI43" s="26"/>
+      <c r="AE43" s="17"/>
+      <c r="AF43" s="25"/>
+      <c r="AG43" s="16"/>
+      <c r="AH43" s="26"/>
+      <c r="AI43" s="25"/>
       <c r="AJ43" s="16"/>
       <c r="AK43" s="16"/>
       <c r="AL43" s="16"/>
@@ -7252,7 +7252,7 @@
       <c r="BW43" s="20"/>
       <c r="BX43" s="20"/>
       <c r="BY43" s="20"/>
-      <c r="CG43" s="20"/>
+      <c r="CH43" s="20"/>
       <c r="CO43" s="27"/>
       <c r="CP43" s="17"/>
       <c r="CQ43" s="17"/>
@@ -7274,14 +7274,14 @@
       <c r="S44" s="20"/>
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
-      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
       <c r="AB44" s="20"/>
       <c r="AC44" s="20"/>
-      <c r="AD44" s="16"/>
-      <c r="AF44" s="17"/>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="25"/>
-      <c r="AI44" s="26"/>
+      <c r="AE44" s="17"/>
+      <c r="AF44" s="25"/>
+      <c r="AG44" s="16"/>
+      <c r="AH44" s="26"/>
+      <c r="AI44" s="25"/>
       <c r="AJ44" s="16"/>
       <c r="AK44" s="16"/>
       <c r="AL44" s="16"/>
@@ -7306,7 +7306,7 @@
       <c r="BW44" s="20"/>
       <c r="BX44" s="20"/>
       <c r="BY44" s="20"/>
-      <c r="CG44" s="20"/>
+      <c r="CH44" s="20"/>
       <c r="CO44" s="27"/>
       <c r="CP44" s="17"/>
       <c r="CQ44" s="17"/>
@@ -7328,14 +7328,14 @@
       <c r="S45" s="20"/>
       <c r="T45" s="20"/>
       <c r="U45" s="20"/>
-      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
       <c r="AB45" s="20"/>
       <c r="AC45" s="20"/>
-      <c r="AD45" s="16"/>
-      <c r="AF45" s="17"/>
-      <c r="AG45" s="25"/>
-      <c r="AH45" s="25"/>
-      <c r="AI45" s="26"/>
+      <c r="AE45" s="17"/>
+      <c r="AF45" s="25"/>
+      <c r="AG45" s="16"/>
+      <c r="AH45" s="26"/>
+      <c r="AI45" s="25"/>
       <c r="AJ45" s="16"/>
       <c r="AK45" s="16"/>
       <c r="AL45" s="16"/>
@@ -7360,7 +7360,7 @@
       <c r="BW45" s="20"/>
       <c r="BX45" s="20"/>
       <c r="BY45" s="20"/>
-      <c r="CG45" s="20"/>
+      <c r="CH45" s="20"/>
       <c r="CO45" s="27"/>
       <c r="CP45" s="17"/>
       <c r="CQ45" s="17"/>
@@ -7382,14 +7382,14 @@
       <c r="S46" s="20"/>
       <c r="T46" s="20"/>
       <c r="U46" s="20"/>
-      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
       <c r="AB46" s="20"/>
       <c r="AC46" s="20"/>
-      <c r="AD46" s="16"/>
-      <c r="AF46" s="17"/>
-      <c r="AG46" s="25"/>
-      <c r="AH46" s="25"/>
-      <c r="AI46" s="26"/>
+      <c r="AE46" s="17"/>
+      <c r="AF46" s="25"/>
+      <c r="AG46" s="16"/>
+      <c r="AH46" s="26"/>
+      <c r="AI46" s="25"/>
       <c r="AJ46" s="16"/>
       <c r="AK46" s="16"/>
       <c r="AL46" s="16"/>
@@ -7414,7 +7414,7 @@
       <c r="BW46" s="20"/>
       <c r="BX46" s="20"/>
       <c r="BY46" s="20"/>
-      <c r="CG46" s="20"/>
+      <c r="CH46" s="20"/>
       <c r="CO46" s="27"/>
       <c r="CP46" s="17"/>
       <c r="CQ46" s="17"/>
@@ -7436,14 +7436,14 @@
       <c r="S47" s="20"/>
       <c r="T47" s="20"/>
       <c r="U47" s="20"/>
-      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
       <c r="AB47" s="20"/>
       <c r="AC47" s="20"/>
-      <c r="AD47" s="16"/>
-      <c r="AF47" s="17"/>
-      <c r="AG47" s="25"/>
-      <c r="AH47" s="25"/>
-      <c r="AI47" s="26"/>
+      <c r="AE47" s="17"/>
+      <c r="AF47" s="25"/>
+      <c r="AG47" s="16"/>
+      <c r="AH47" s="26"/>
+      <c r="AI47" s="25"/>
       <c r="AJ47" s="16"/>
       <c r="AK47" s="16"/>
       <c r="AL47" s="16"/>
@@ -7468,7 +7468,7 @@
       <c r="BW47" s="20"/>
       <c r="BX47" s="20"/>
       <c r="BY47" s="20"/>
-      <c r="CG47" s="20"/>
+      <c r="CH47" s="20"/>
       <c r="CO47" s="27"/>
       <c r="CP47" s="17"/>
       <c r="CQ47" s="17"/>
@@ -7490,14 +7490,14 @@
       <c r="S48" s="20"/>
       <c r="T48" s="20"/>
       <c r="U48" s="20"/>
-      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
       <c r="AB48" s="20"/>
       <c r="AC48" s="20"/>
-      <c r="AD48" s="16"/>
-      <c r="AF48" s="17"/>
-      <c r="AG48" s="25"/>
-      <c r="AH48" s="25"/>
-      <c r="AI48" s="26"/>
+      <c r="AE48" s="17"/>
+      <c r="AF48" s="25"/>
+      <c r="AG48" s="16"/>
+      <c r="AH48" s="26"/>
+      <c r="AI48" s="25"/>
       <c r="AJ48" s="16"/>
       <c r="AK48" s="16"/>
       <c r="AL48" s="16"/>
@@ -7522,7 +7522,7 @@
       <c r="BW48" s="20"/>
       <c r="BX48" s="20"/>
       <c r="BY48" s="20"/>
-      <c r="CG48" s="20"/>
+      <c r="CH48" s="20"/>
       <c r="CO48" s="27"/>
       <c r="CP48" s="17"/>
       <c r="CQ48" s="17"/>
@@ -7544,14 +7544,14 @@
       <c r="S49" s="20"/>
       <c r="T49" s="20"/>
       <c r="U49" s="20"/>
-      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
       <c r="AB49" s="20"/>
       <c r="AC49" s="20"/>
-      <c r="AD49" s="16"/>
-      <c r="AF49" s="17"/>
-      <c r="AG49" s="25"/>
-      <c r="AH49" s="25"/>
-      <c r="AI49" s="26"/>
+      <c r="AE49" s="17"/>
+      <c r="AF49" s="25"/>
+      <c r="AG49" s="16"/>
+      <c r="AH49" s="26"/>
+      <c r="AI49" s="25"/>
       <c r="AJ49" s="16"/>
       <c r="AK49" s="16"/>
       <c r="AL49" s="16"/>
@@ -7576,7 +7576,7 @@
       <c r="BW49" s="20"/>
       <c r="BX49" s="20"/>
       <c r="BY49" s="20"/>
-      <c r="CG49" s="20"/>
+      <c r="CH49" s="20"/>
       <c r="CO49" s="27"/>
       <c r="CP49" s="17"/>
       <c r="CQ49" s="17"/>
@@ -7598,14 +7598,14 @@
       <c r="S50" s="20"/>
       <c r="T50" s="20"/>
       <c r="U50" s="20"/>
-      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
       <c r="AB50" s="20"/>
       <c r="AC50" s="20"/>
-      <c r="AD50" s="16"/>
-      <c r="AF50" s="17"/>
-      <c r="AG50" s="25"/>
-      <c r="AH50" s="25"/>
-      <c r="AI50" s="26"/>
+      <c r="AE50" s="17"/>
+      <c r="AF50" s="25"/>
+      <c r="AG50" s="16"/>
+      <c r="AH50" s="26"/>
+      <c r="AI50" s="25"/>
       <c r="AJ50" s="16"/>
       <c r="AK50" s="16"/>
       <c r="AL50" s="16"/>
@@ -7630,7 +7630,7 @@
       <c r="BW50" s="20"/>
       <c r="BX50" s="20"/>
       <c r="BY50" s="20"/>
-      <c r="CG50" s="20"/>
+      <c r="CH50" s="20"/>
       <c r="CO50" s="27"/>
       <c r="CP50" s="17"/>
       <c r="CQ50" s="17"/>
@@ -7652,14 +7652,14 @@
       <c r="S51" s="20"/>
       <c r="T51" s="20"/>
       <c r="U51" s="20"/>
-      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
       <c r="AB51" s="20"/>
       <c r="AC51" s="20"/>
-      <c r="AD51" s="16"/>
-      <c r="AF51" s="17"/>
-      <c r="AG51" s="25"/>
-      <c r="AH51" s="25"/>
-      <c r="AI51" s="26"/>
+      <c r="AE51" s="17"/>
+      <c r="AF51" s="25"/>
+      <c r="AG51" s="16"/>
+      <c r="AH51" s="26"/>
+      <c r="AI51" s="25"/>
       <c r="AJ51" s="16"/>
       <c r="AK51" s="16"/>
       <c r="AL51" s="16"/>
@@ -7684,7 +7684,7 @@
       <c r="BW51" s="20"/>
       <c r="BX51" s="20"/>
       <c r="BY51" s="20"/>
-      <c r="CG51" s="20"/>
+      <c r="CH51" s="20"/>
       <c r="CO51" s="27"/>
       <c r="CP51" s="17"/>
       <c r="CQ51" s="17"/>
@@ -7706,14 +7706,14 @@
       <c r="S52" s="20"/>
       <c r="T52" s="20"/>
       <c r="U52" s="20"/>
-      <c r="X52" s="20"/>
+      <c r="Y52" s="20"/>
       <c r="AB52" s="20"/>
       <c r="AC52" s="20"/>
-      <c r="AD52" s="16"/>
-      <c r="AF52" s="17"/>
-      <c r="AG52" s="25"/>
-      <c r="AH52" s="25"/>
-      <c r="AI52" s="26"/>
+      <c r="AE52" s="17"/>
+      <c r="AF52" s="25"/>
+      <c r="AG52" s="16"/>
+      <c r="AH52" s="26"/>
+      <c r="AI52" s="25"/>
       <c r="AJ52" s="16"/>
       <c r="AK52" s="16"/>
       <c r="AL52" s="16"/>
@@ -7738,7 +7738,7 @@
       <c r="BW52" s="20"/>
       <c r="BX52" s="20"/>
       <c r="BY52" s="20"/>
-      <c r="CG52" s="20"/>
+      <c r="CH52" s="20"/>
       <c r="CO52" s="27"/>
       <c r="CP52" s="17"/>
       <c r="CQ52" s="17"/>
@@ -7760,14 +7760,14 @@
       <c r="S53" s="20"/>
       <c r="T53" s="20"/>
       <c r="U53" s="20"/>
-      <c r="X53" s="20"/>
+      <c r="Y53" s="20"/>
       <c r="AB53" s="20"/>
       <c r="AC53" s="20"/>
-      <c r="AD53" s="16"/>
-      <c r="AF53" s="17"/>
-      <c r="AG53" s="25"/>
-      <c r="AH53" s="25"/>
-      <c r="AI53" s="26"/>
+      <c r="AE53" s="17"/>
+      <c r="AF53" s="25"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="26"/>
+      <c r="AI53" s="25"/>
       <c r="AJ53" s="16"/>
       <c r="AK53" s="16"/>
       <c r="AL53" s="16"/>
@@ -7792,7 +7792,7 @@
       <c r="BW53" s="20"/>
       <c r="BX53" s="20"/>
       <c r="BY53" s="20"/>
-      <c r="CG53" s="20"/>
+      <c r="CH53" s="20"/>
       <c r="CO53" s="27"/>
       <c r="CP53" s="17"/>
       <c r="CQ53" s="17"/>
@@ -7814,14 +7814,14 @@
       <c r="S54" s="20"/>
       <c r="T54" s="20"/>
       <c r="U54" s="20"/>
-      <c r="X54" s="20"/>
+      <c r="Y54" s="20"/>
       <c r="AB54" s="20"/>
       <c r="AC54" s="20"/>
-      <c r="AD54" s="16"/>
-      <c r="AF54" s="17"/>
-      <c r="AG54" s="25"/>
-      <c r="AH54" s="25"/>
-      <c r="AI54" s="26"/>
+      <c r="AE54" s="17"/>
+      <c r="AF54" s="25"/>
+      <c r="AG54" s="16"/>
+      <c r="AH54" s="26"/>
+      <c r="AI54" s="25"/>
       <c r="AJ54" s="16"/>
       <c r="AK54" s="16"/>
       <c r="AL54" s="16"/>
@@ -7846,7 +7846,7 @@
       <c r="BW54" s="20"/>
       <c r="BX54" s="20"/>
       <c r="BY54" s="20"/>
-      <c r="CG54" s="20"/>
+      <c r="CH54" s="20"/>
       <c r="CO54" s="27"/>
       <c r="CP54" s="17"/>
       <c r="CQ54" s="17"/>
@@ -7868,14 +7868,14 @@
       <c r="S55" s="20"/>
       <c r="T55" s="20"/>
       <c r="U55" s="20"/>
-      <c r="X55" s="20"/>
+      <c r="Y55" s="20"/>
       <c r="AB55" s="20"/>
       <c r="AC55" s="20"/>
-      <c r="AD55" s="16"/>
-      <c r="AF55" s="17"/>
-      <c r="AG55" s="25"/>
-      <c r="AH55" s="25"/>
-      <c r="AI55" s="26"/>
+      <c r="AE55" s="17"/>
+      <c r="AF55" s="25"/>
+      <c r="AG55" s="16"/>
+      <c r="AH55" s="26"/>
+      <c r="AI55" s="25"/>
       <c r="AJ55" s="16"/>
       <c r="AK55" s="16"/>
       <c r="AL55" s="16"/>
@@ -7900,7 +7900,7 @@
       <c r="BW55" s="20"/>
       <c r="BX55" s="20"/>
       <c r="BY55" s="20"/>
-      <c r="CG55" s="20"/>
+      <c r="CH55" s="20"/>
       <c r="CO55" s="27"/>
       <c r="CP55" s="17"/>
       <c r="CQ55" s="17"/>
@@ -7922,14 +7922,14 @@
       <c r="S56" s="20"/>
       <c r="T56" s="20"/>
       <c r="U56" s="20"/>
-      <c r="X56" s="20"/>
+      <c r="Y56" s="20"/>
       <c r="AB56" s="20"/>
       <c r="AC56" s="20"/>
-      <c r="AD56" s="16"/>
-      <c r="AF56" s="17"/>
-      <c r="AG56" s="25"/>
-      <c r="AH56" s="25"/>
-      <c r="AI56" s="26"/>
+      <c r="AE56" s="17"/>
+      <c r="AF56" s="25"/>
+      <c r="AG56" s="16"/>
+      <c r="AH56" s="26"/>
+      <c r="AI56" s="25"/>
       <c r="AJ56" s="16"/>
       <c r="AK56" s="16"/>
       <c r="AL56" s="16"/>
@@ -7954,7 +7954,7 @@
       <c r="BW56" s="20"/>
       <c r="BX56" s="20"/>
       <c r="BY56" s="20"/>
-      <c r="CG56" s="20"/>
+      <c r="CH56" s="20"/>
       <c r="CO56" s="27"/>
       <c r="CP56" s="17"/>
       <c r="CQ56" s="17"/>
@@ -7976,14 +7976,14 @@
       <c r="S57" s="20"/>
       <c r="T57" s="20"/>
       <c r="U57" s="20"/>
-      <c r="X57" s="20"/>
+      <c r="Y57" s="20"/>
       <c r="AB57" s="20"/>
       <c r="AC57" s="20"/>
-      <c r="AD57" s="16"/>
-      <c r="AF57" s="17"/>
-      <c r="AG57" s="25"/>
-      <c r="AH57" s="25"/>
-      <c r="AI57" s="26"/>
+      <c r="AE57" s="17"/>
+      <c r="AF57" s="25"/>
+      <c r="AG57" s="16"/>
+      <c r="AH57" s="26"/>
+      <c r="AI57" s="25"/>
       <c r="AJ57" s="16"/>
       <c r="AK57" s="16"/>
       <c r="AL57" s="16"/>
@@ -8008,7 +8008,7 @@
       <c r="BW57" s="20"/>
       <c r="BX57" s="20"/>
       <c r="BY57" s="20"/>
-      <c r="CG57" s="20"/>
+      <c r="CH57" s="20"/>
       <c r="CO57" s="27"/>
       <c r="CP57" s="17"/>
       <c r="CQ57" s="17"/>
@@ -8030,14 +8030,14 @@
       <c r="S58" s="20"/>
       <c r="T58" s="20"/>
       <c r="U58" s="20"/>
-      <c r="X58" s="20"/>
+      <c r="Y58" s="20"/>
       <c r="AB58" s="20"/>
       <c r="AC58" s="20"/>
-      <c r="AD58" s="16"/>
-      <c r="AF58" s="17"/>
-      <c r="AG58" s="25"/>
-      <c r="AH58" s="25"/>
-      <c r="AI58" s="26"/>
+      <c r="AE58" s="17"/>
+      <c r="AF58" s="25"/>
+      <c r="AG58" s="16"/>
+      <c r="AH58" s="26"/>
+      <c r="AI58" s="25"/>
       <c r="AJ58" s="16"/>
       <c r="AK58" s="16"/>
       <c r="AL58" s="16"/>
@@ -8062,7 +8062,7 @@
       <c r="BW58" s="20"/>
       <c r="BX58" s="20"/>
       <c r="BY58" s="20"/>
-      <c r="CG58" s="20"/>
+      <c r="CH58" s="20"/>
       <c r="CO58" s="27"/>
       <c r="CP58" s="17"/>
       <c r="CQ58" s="17"/>
@@ -8084,14 +8084,14 @@
       <c r="S59" s="20"/>
       <c r="T59" s="20"/>
       <c r="U59" s="20"/>
-      <c r="X59" s="20"/>
+      <c r="Y59" s="20"/>
       <c r="AB59" s="20"/>
       <c r="AC59" s="20"/>
-      <c r="AD59" s="16"/>
-      <c r="AF59" s="17"/>
-      <c r="AG59" s="25"/>
-      <c r="AH59" s="25"/>
-      <c r="AI59" s="26"/>
+      <c r="AE59" s="17"/>
+      <c r="AF59" s="25"/>
+      <c r="AG59" s="16"/>
+      <c r="AH59" s="26"/>
+      <c r="AI59" s="25"/>
       <c r="AJ59" s="16"/>
       <c r="AK59" s="16"/>
       <c r="AL59" s="16"/>
@@ -8116,7 +8116,7 @@
       <c r="BW59" s="20"/>
       <c r="BX59" s="20"/>
       <c r="BY59" s="20"/>
-      <c r="CG59" s="20"/>
+      <c r="CH59" s="20"/>
       <c r="CO59" s="27"/>
       <c r="CP59" s="17"/>
       <c r="CQ59" s="17"/>
@@ -8138,14 +8138,14 @@
       <c r="S60" s="20"/>
       <c r="T60" s="20"/>
       <c r="U60" s="20"/>
-      <c r="X60" s="20"/>
+      <c r="Y60" s="20"/>
       <c r="AB60" s="20"/>
       <c r="AC60" s="20"/>
-      <c r="AD60" s="16"/>
-      <c r="AF60" s="17"/>
-      <c r="AG60" s="25"/>
-      <c r="AH60" s="25"/>
-      <c r="AI60" s="26"/>
+      <c r="AE60" s="17"/>
+      <c r="AF60" s="25"/>
+      <c r="AG60" s="16"/>
+      <c r="AH60" s="26"/>
+      <c r="AI60" s="25"/>
       <c r="AJ60" s="16"/>
       <c r="AK60" s="16"/>
       <c r="AL60" s="16"/>
@@ -8170,7 +8170,7 @@
       <c r="BW60" s="20"/>
       <c r="BX60" s="20"/>
       <c r="BY60" s="20"/>
-      <c r="CG60" s="20"/>
+      <c r="CH60" s="20"/>
       <c r="CO60" s="27"/>
       <c r="CP60" s="17"/>
       <c r="CQ60" s="17"/>
@@ -8192,14 +8192,14 @@
       <c r="S61" s="20"/>
       <c r="T61" s="20"/>
       <c r="U61" s="20"/>
-      <c r="X61" s="20"/>
+      <c r="Y61" s="20"/>
       <c r="AB61" s="20"/>
       <c r="AC61" s="20"/>
-      <c r="AD61" s="16"/>
-      <c r="AF61" s="17"/>
-      <c r="AG61" s="25"/>
-      <c r="AH61" s="25"/>
-      <c r="AI61" s="26"/>
+      <c r="AE61" s="17"/>
+      <c r="AF61" s="25"/>
+      <c r="AG61" s="16"/>
+      <c r="AH61" s="26"/>
+      <c r="AI61" s="25"/>
       <c r="AJ61" s="16"/>
       <c r="AK61" s="16"/>
       <c r="AL61" s="16"/>
@@ -8224,7 +8224,7 @@
       <c r="BW61" s="20"/>
       <c r="BX61" s="20"/>
       <c r="BY61" s="20"/>
-      <c r="CG61" s="20"/>
+      <c r="CH61" s="20"/>
       <c r="CO61" s="27"/>
       <c r="CP61" s="17"/>
       <c r="CQ61" s="17"/>
@@ -8246,14 +8246,14 @@
       <c r="S62" s="20"/>
       <c r="T62" s="20"/>
       <c r="U62" s="20"/>
-      <c r="X62" s="20"/>
+      <c r="Y62" s="20"/>
       <c r="AB62" s="20"/>
       <c r="AC62" s="20"/>
-      <c r="AD62" s="16"/>
-      <c r="AF62" s="17"/>
-      <c r="AG62" s="25"/>
-      <c r="AH62" s="25"/>
-      <c r="AI62" s="26"/>
+      <c r="AE62" s="17"/>
+      <c r="AF62" s="25"/>
+      <c r="AG62" s="16"/>
+      <c r="AH62" s="26"/>
+      <c r="AI62" s="25"/>
       <c r="AJ62" s="16"/>
       <c r="AK62" s="16"/>
       <c r="AL62" s="16"/>
@@ -8278,7 +8278,7 @@
       <c r="BW62" s="20"/>
       <c r="BX62" s="20"/>
       <c r="BY62" s="20"/>
-      <c r="CG62" s="20"/>
+      <c r="CH62" s="20"/>
       <c r="CO62" s="27"/>
       <c r="CP62" s="17"/>
       <c r="CQ62" s="17"/>
@@ -8300,14 +8300,14 @@
       <c r="S63" s="20"/>
       <c r="T63" s="20"/>
       <c r="U63" s="20"/>
-      <c r="X63" s="20"/>
+      <c r="Y63" s="20"/>
       <c r="AB63" s="20"/>
       <c r="AC63" s="20"/>
-      <c r="AD63" s="16"/>
-      <c r="AF63" s="17"/>
-      <c r="AG63" s="25"/>
-      <c r="AH63" s="25"/>
-      <c r="AI63" s="26"/>
+      <c r="AE63" s="17"/>
+      <c r="AF63" s="25"/>
+      <c r="AG63" s="16"/>
+      <c r="AH63" s="26"/>
+      <c r="AI63" s="25"/>
       <c r="AJ63" s="16"/>
       <c r="AK63" s="16"/>
       <c r="AL63" s="16"/>
@@ -8332,7 +8332,7 @@
       <c r="BW63" s="20"/>
       <c r="BX63" s="20"/>
       <c r="BY63" s="20"/>
-      <c r="CG63" s="20"/>
+      <c r="CH63" s="20"/>
       <c r="CO63" s="27"/>
       <c r="CP63" s="17"/>
       <c r="CQ63" s="17"/>
@@ -8354,14 +8354,14 @@
       <c r="S64" s="20"/>
       <c r="T64" s="20"/>
       <c r="U64" s="20"/>
-      <c r="X64" s="20"/>
+      <c r="Y64" s="20"/>
       <c r="AB64" s="20"/>
       <c r="AC64" s="20"/>
-      <c r="AD64" s="16"/>
-      <c r="AF64" s="17"/>
-      <c r="AG64" s="25"/>
-      <c r="AH64" s="25"/>
-      <c r="AI64" s="26"/>
+      <c r="AE64" s="17"/>
+      <c r="AF64" s="25"/>
+      <c r="AG64" s="16"/>
+      <c r="AH64" s="26"/>
+      <c r="AI64" s="25"/>
       <c r="AJ64" s="16"/>
       <c r="AK64" s="16"/>
       <c r="AL64" s="16"/>
@@ -8386,7 +8386,7 @@
       <c r="BW64" s="20"/>
       <c r="BX64" s="20"/>
       <c r="BY64" s="20"/>
-      <c r="CG64" s="20"/>
+      <c r="CH64" s="20"/>
       <c r="CO64" s="27"/>
       <c r="CP64" s="17"/>
       <c r="CQ64" s="17"/>
@@ -8408,14 +8408,14 @@
       <c r="S65" s="20"/>
       <c r="T65" s="20"/>
       <c r="U65" s="20"/>
-      <c r="X65" s="20"/>
+      <c r="Y65" s="20"/>
       <c r="AB65" s="20"/>
       <c r="AC65" s="20"/>
-      <c r="AD65" s="16"/>
-      <c r="AF65" s="17"/>
-      <c r="AG65" s="25"/>
-      <c r="AH65" s="25"/>
-      <c r="AI65" s="26"/>
+      <c r="AE65" s="17"/>
+      <c r="AF65" s="25"/>
+      <c r="AG65" s="16"/>
+      <c r="AH65" s="26"/>
+      <c r="AI65" s="25"/>
       <c r="AJ65" s="16"/>
       <c r="AK65" s="16"/>
       <c r="AL65" s="16"/>
@@ -8440,7 +8440,7 @@
       <c r="BW65" s="20"/>
       <c r="BX65" s="20"/>
       <c r="BY65" s="20"/>
-      <c r="CG65" s="20"/>
+      <c r="CH65" s="20"/>
       <c r="CO65" s="27"/>
       <c r="CP65" s="17"/>
       <c r="CQ65" s="17"/>
@@ -8462,14 +8462,14 @@
       <c r="S66" s="20"/>
       <c r="T66" s="20"/>
       <c r="U66" s="20"/>
-      <c r="X66" s="20"/>
+      <c r="Y66" s="20"/>
       <c r="AB66" s="20"/>
       <c r="AC66" s="20"/>
-      <c r="AD66" s="16"/>
-      <c r="AF66" s="17"/>
-      <c r="AG66" s="25"/>
-      <c r="AH66" s="25"/>
-      <c r="AI66" s="26"/>
+      <c r="AE66" s="17"/>
+      <c r="AF66" s="25"/>
+      <c r="AG66" s="16"/>
+      <c r="AH66" s="26"/>
+      <c r="AI66" s="25"/>
       <c r="AJ66" s="16"/>
       <c r="AK66" s="16"/>
       <c r="AL66" s="16"/>
@@ -8494,7 +8494,7 @@
       <c r="BW66" s="20"/>
       <c r="BX66" s="20"/>
       <c r="BY66" s="20"/>
-      <c r="CG66" s="20"/>
+      <c r="CH66" s="20"/>
       <c r="CO66" s="27"/>
       <c r="CP66" s="17"/>
       <c r="CQ66" s="17"/>
@@ -8516,14 +8516,14 @@
       <c r="S67" s="20"/>
       <c r="T67" s="20"/>
       <c r="U67" s="20"/>
-      <c r="X67" s="20"/>
+      <c r="Y67" s="20"/>
       <c r="AB67" s="20"/>
       <c r="AC67" s="20"/>
-      <c r="AD67" s="16"/>
-      <c r="AF67" s="17"/>
-      <c r="AG67" s="25"/>
-      <c r="AH67" s="25"/>
-      <c r="AI67" s="26"/>
+      <c r="AE67" s="17"/>
+      <c r="AF67" s="25"/>
+      <c r="AG67" s="16"/>
+      <c r="AH67" s="26"/>
+      <c r="AI67" s="25"/>
       <c r="AJ67" s="16"/>
       <c r="AK67" s="16"/>
       <c r="AL67" s="16"/>
@@ -8548,7 +8548,7 @@
       <c r="BW67" s="20"/>
       <c r="BX67" s="20"/>
       <c r="BY67" s="20"/>
-      <c r="CG67" s="20"/>
+      <c r="CH67" s="20"/>
       <c r="CO67" s="27"/>
       <c r="CP67" s="17"/>
       <c r="CQ67" s="17"/>
@@ -8570,14 +8570,14 @@
       <c r="S68" s="20"/>
       <c r="T68" s="20"/>
       <c r="U68" s="20"/>
-      <c r="X68" s="20"/>
+      <c r="Y68" s="20"/>
       <c r="AB68" s="20"/>
       <c r="AC68" s="20"/>
-      <c r="AD68" s="16"/>
-      <c r="AF68" s="17"/>
-      <c r="AG68" s="25"/>
-      <c r="AH68" s="25"/>
-      <c r="AI68" s="26"/>
+      <c r="AE68" s="17"/>
+      <c r="AF68" s="25"/>
+      <c r="AG68" s="16"/>
+      <c r="AH68" s="26"/>
+      <c r="AI68" s="25"/>
       <c r="AJ68" s="16"/>
       <c r="AK68" s="16"/>
       <c r="AL68" s="16"/>
@@ -8602,7 +8602,7 @@
       <c r="BW68" s="20"/>
       <c r="BX68" s="20"/>
       <c r="BY68" s="20"/>
-      <c r="CG68" s="20"/>
+      <c r="CH68" s="20"/>
       <c r="CO68" s="27"/>
       <c r="CP68" s="17"/>
       <c r="CQ68" s="17"/>
@@ -8624,14 +8624,14 @@
       <c r="S69" s="20"/>
       <c r="T69" s="20"/>
       <c r="U69" s="20"/>
-      <c r="X69" s="20"/>
+      <c r="Y69" s="20"/>
       <c r="AB69" s="20"/>
       <c r="AC69" s="20"/>
-      <c r="AD69" s="16"/>
-      <c r="AF69" s="17"/>
-      <c r="AG69" s="25"/>
-      <c r="AH69" s="25"/>
-      <c r="AI69" s="26"/>
+      <c r="AE69" s="17"/>
+      <c r="AF69" s="25"/>
+      <c r="AG69" s="16"/>
+      <c r="AH69" s="26"/>
+      <c r="AI69" s="25"/>
       <c r="AJ69" s="16"/>
       <c r="AK69" s="16"/>
       <c r="AL69" s="16"/>
@@ -8656,7 +8656,7 @@
       <c r="BW69" s="20"/>
       <c r="BX69" s="20"/>
       <c r="BY69" s="20"/>
-      <c r="CG69" s="20"/>
+      <c r="CH69" s="20"/>
       <c r="CO69" s="27"/>
       <c r="CP69" s="17"/>
       <c r="CQ69" s="17"/>
@@ -8678,14 +8678,14 @@
       <c r="S70" s="20"/>
       <c r="T70" s="20"/>
       <c r="U70" s="20"/>
-      <c r="X70" s="20"/>
+      <c r="Y70" s="20"/>
       <c r="AB70" s="20"/>
       <c r="AC70" s="20"/>
-      <c r="AD70" s="16"/>
-      <c r="AF70" s="17"/>
-      <c r="AG70" s="25"/>
-      <c r="AH70" s="25"/>
-      <c r="AI70" s="26"/>
+      <c r="AE70" s="17"/>
+      <c r="AF70" s="25"/>
+      <c r="AG70" s="16"/>
+      <c r="AH70" s="26"/>
+      <c r="AI70" s="25"/>
       <c r="AJ70" s="16"/>
       <c r="AK70" s="16"/>
       <c r="AL70" s="16"/>
@@ -8710,7 +8710,7 @@
       <c r="BW70" s="20"/>
       <c r="BX70" s="20"/>
       <c r="BY70" s="20"/>
-      <c r="CG70" s="20"/>
+      <c r="CH70" s="20"/>
       <c r="CO70" s="27"/>
       <c r="CP70" s="17"/>
       <c r="CQ70" s="17"/>
@@ -8732,14 +8732,14 @@
       <c r="S71" s="20"/>
       <c r="T71" s="20"/>
       <c r="U71" s="20"/>
-      <c r="X71" s="20"/>
+      <c r="Y71" s="20"/>
       <c r="AB71" s="20"/>
       <c r="AC71" s="20"/>
-      <c r="AD71" s="16"/>
-      <c r="AF71" s="17"/>
-      <c r="AG71" s="25"/>
-      <c r="AH71" s="25"/>
-      <c r="AI71" s="26"/>
+      <c r="AE71" s="17"/>
+      <c r="AF71" s="25"/>
+      <c r="AG71" s="16"/>
+      <c r="AH71" s="26"/>
+      <c r="AI71" s="25"/>
       <c r="AJ71" s="16"/>
       <c r="AK71" s="16"/>
       <c r="AL71" s="16"/>
@@ -8764,7 +8764,7 @@
       <c r="BW71" s="20"/>
       <c r="BX71" s="20"/>
       <c r="BY71" s="20"/>
-      <c r="CG71" s="20"/>
+      <c r="CH71" s="20"/>
       <c r="CO71" s="27"/>
       <c r="CP71" s="17"/>
       <c r="CQ71" s="17"/>
@@ -8786,14 +8786,14 @@
       <c r="S72" s="20"/>
       <c r="T72" s="20"/>
       <c r="U72" s="20"/>
-      <c r="X72" s="20"/>
+      <c r="Y72" s="20"/>
       <c r="AB72" s="20"/>
       <c r="AC72" s="20"/>
-      <c r="AD72" s="16"/>
-      <c r="AF72" s="17"/>
-      <c r="AG72" s="25"/>
-      <c r="AH72" s="25"/>
-      <c r="AI72" s="26"/>
+      <c r="AE72" s="17"/>
+      <c r="AF72" s="25"/>
+      <c r="AG72" s="16"/>
+      <c r="AH72" s="26"/>
+      <c r="AI72" s="25"/>
       <c r="AJ72" s="16"/>
       <c r="AK72" s="16"/>
       <c r="AL72" s="16"/>
@@ -8818,7 +8818,7 @@
       <c r="BW72" s="20"/>
       <c r="BX72" s="20"/>
       <c r="BY72" s="20"/>
-      <c r="CG72" s="20"/>
+      <c r="CH72" s="20"/>
       <c r="CO72" s="27"/>
       <c r="CP72" s="17"/>
       <c r="CQ72" s="17"/>
@@ -8840,14 +8840,14 @@
       <c r="S73" s="20"/>
       <c r="T73" s="20"/>
       <c r="U73" s="20"/>
-      <c r="X73" s="20"/>
+      <c r="Y73" s="20"/>
       <c r="AB73" s="20"/>
       <c r="AC73" s="20"/>
-      <c r="AD73" s="16"/>
-      <c r="AF73" s="17"/>
-      <c r="AG73" s="25"/>
-      <c r="AH73" s="25"/>
-      <c r="AI73" s="26"/>
+      <c r="AE73" s="17"/>
+      <c r="AF73" s="25"/>
+      <c r="AG73" s="16"/>
+      <c r="AH73" s="26"/>
+      <c r="AI73" s="25"/>
       <c r="AJ73" s="16"/>
       <c r="AK73" s="16"/>
       <c r="AL73" s="16"/>
@@ -8872,7 +8872,7 @@
       <c r="BW73" s="20"/>
       <c r="BX73" s="20"/>
       <c r="BY73" s="20"/>
-      <c r="CG73" s="20"/>
+      <c r="CH73" s="20"/>
       <c r="CO73" s="27"/>
       <c r="CP73" s="17"/>
       <c r="CQ73" s="17"/>
@@ -8894,14 +8894,14 @@
       <c r="S74" s="20"/>
       <c r="T74" s="20"/>
       <c r="U74" s="20"/>
-      <c r="X74" s="20"/>
+      <c r="Y74" s="20"/>
       <c r="AB74" s="20"/>
       <c r="AC74" s="20"/>
-      <c r="AD74" s="16"/>
-      <c r="AF74" s="17"/>
-      <c r="AG74" s="25"/>
-      <c r="AH74" s="25"/>
-      <c r="AI74" s="26"/>
+      <c r="AE74" s="17"/>
+      <c r="AF74" s="25"/>
+      <c r="AG74" s="16"/>
+      <c r="AH74" s="26"/>
+      <c r="AI74" s="25"/>
       <c r="AJ74" s="16"/>
       <c r="AK74" s="16"/>
       <c r="AL74" s="16"/>
@@ -8926,7 +8926,7 @@
       <c r="BW74" s="20"/>
       <c r="BX74" s="20"/>
       <c r="BY74" s="20"/>
-      <c r="CG74" s="20"/>
+      <c r="CH74" s="20"/>
       <c r="CO74" s="27"/>
       <c r="CP74" s="17"/>
       <c r="CQ74" s="17"/>
@@ -8948,14 +8948,14 @@
       <c r="S75" s="20"/>
       <c r="T75" s="20"/>
       <c r="U75" s="20"/>
-      <c r="X75" s="20"/>
+      <c r="Y75" s="20"/>
       <c r="AB75" s="20"/>
       <c r="AC75" s="20"/>
-      <c r="AD75" s="16"/>
-      <c r="AF75" s="17"/>
-      <c r="AG75" s="25"/>
-      <c r="AH75" s="25"/>
-      <c r="AI75" s="26"/>
+      <c r="AE75" s="17"/>
+      <c r="AF75" s="25"/>
+      <c r="AG75" s="16"/>
+      <c r="AH75" s="26"/>
+      <c r="AI75" s="25"/>
       <c r="AJ75" s="16"/>
       <c r="AK75" s="16"/>
       <c r="AL75" s="16"/>
@@ -8980,7 +8980,7 @@
       <c r="BW75" s="20"/>
       <c r="BX75" s="20"/>
       <c r="BY75" s="20"/>
-      <c r="CG75" s="20"/>
+      <c r="CH75" s="20"/>
       <c r="CO75" s="27"/>
       <c r="CP75" s="17"/>
       <c r="CQ75" s="17"/>
@@ -9002,14 +9002,14 @@
       <c r="S76" s="20"/>
       <c r="T76" s="20"/>
       <c r="U76" s="20"/>
-      <c r="X76" s="20"/>
+      <c r="Y76" s="20"/>
       <c r="AB76" s="20"/>
       <c r="AC76" s="20"/>
-      <c r="AD76" s="16"/>
-      <c r="AF76" s="17"/>
-      <c r="AG76" s="25"/>
-      <c r="AH76" s="25"/>
-      <c r="AI76" s="26"/>
+      <c r="AE76" s="17"/>
+      <c r="AF76" s="25"/>
+      <c r="AG76" s="16"/>
+      <c r="AH76" s="26"/>
+      <c r="AI76" s="25"/>
       <c r="AJ76" s="16"/>
       <c r="AK76" s="16"/>
       <c r="AL76" s="16"/>
@@ -9034,7 +9034,7 @@
       <c r="BW76" s="20"/>
       <c r="BX76" s="20"/>
       <c r="BY76" s="20"/>
-      <c r="CG76" s="20"/>
+      <c r="CH76" s="20"/>
       <c r="CO76" s="27"/>
       <c r="CP76" s="17"/>
       <c r="CQ76" s="17"/>
@@ -9056,14 +9056,14 @@
       <c r="S77" s="20"/>
       <c r="T77" s="20"/>
       <c r="U77" s="20"/>
-      <c r="X77" s="20"/>
+      <c r="Y77" s="20"/>
       <c r="AB77" s="20"/>
       <c r="AC77" s="20"/>
-      <c r="AD77" s="16"/>
-      <c r="AF77" s="17"/>
-      <c r="AG77" s="25"/>
-      <c r="AH77" s="25"/>
-      <c r="AI77" s="26"/>
+      <c r="AE77" s="17"/>
+      <c r="AF77" s="25"/>
+      <c r="AG77" s="16"/>
+      <c r="AH77" s="26"/>
+      <c r="AI77" s="25"/>
       <c r="AJ77" s="16"/>
       <c r="AK77" s="16"/>
       <c r="AL77" s="16"/>
@@ -9088,7 +9088,7 @@
       <c r="BW77" s="20"/>
       <c r="BX77" s="20"/>
       <c r="BY77" s="20"/>
-      <c r="CG77" s="20"/>
+      <c r="CH77" s="20"/>
       <c r="CO77" s="27"/>
       <c r="CP77" s="17"/>
       <c r="CQ77" s="17"/>
@@ -9110,14 +9110,14 @@
       <c r="S78" s="20"/>
       <c r="T78" s="20"/>
       <c r="U78" s="20"/>
-      <c r="X78" s="20"/>
+      <c r="Y78" s="20"/>
       <c r="AB78" s="20"/>
       <c r="AC78" s="20"/>
-      <c r="AD78" s="16"/>
-      <c r="AF78" s="17"/>
-      <c r="AG78" s="25"/>
-      <c r="AH78" s="25"/>
-      <c r="AI78" s="26"/>
+      <c r="AE78" s="17"/>
+      <c r="AF78" s="25"/>
+      <c r="AG78" s="16"/>
+      <c r="AH78" s="26"/>
+      <c r="AI78" s="25"/>
       <c r="AJ78" s="16"/>
       <c r="AK78" s="16"/>
       <c r="AL78" s="16"/>
@@ -9142,7 +9142,7 @@
       <c r="BW78" s="20"/>
       <c r="BX78" s="20"/>
       <c r="BY78" s="20"/>
-      <c r="CG78" s="20"/>
+      <c r="CH78" s="20"/>
       <c r="CO78" s="27"/>
       <c r="CP78" s="17"/>
       <c r="CQ78" s="17"/>
@@ -9164,14 +9164,14 @@
       <c r="S79" s="20"/>
       <c r="T79" s="20"/>
       <c r="U79" s="20"/>
-      <c r="X79" s="20"/>
+      <c r="Y79" s="20"/>
       <c r="AB79" s="20"/>
       <c r="AC79" s="20"/>
-      <c r="AD79" s="16"/>
-      <c r="AF79" s="17"/>
-      <c r="AG79" s="25"/>
-      <c r="AH79" s="25"/>
-      <c r="AI79" s="26"/>
+      <c r="AE79" s="17"/>
+      <c r="AF79" s="25"/>
+      <c r="AG79" s="16"/>
+      <c r="AH79" s="26"/>
+      <c r="AI79" s="25"/>
       <c r="AJ79" s="16"/>
       <c r="AK79" s="16"/>
       <c r="AL79" s="16"/>
@@ -9196,7 +9196,7 @@
       <c r="BW79" s="20"/>
       <c r="BX79" s="20"/>
       <c r="BY79" s="20"/>
-      <c r="CG79" s="20"/>
+      <c r="CH79" s="20"/>
       <c r="CO79" s="27"/>
       <c r="CP79" s="17"/>
       <c r="CQ79" s="17"/>
@@ -9218,14 +9218,14 @@
       <c r="S80" s="20"/>
       <c r="T80" s="20"/>
       <c r="U80" s="20"/>
-      <c r="X80" s="20"/>
+      <c r="Y80" s="20"/>
       <c r="AB80" s="20"/>
       <c r="AC80" s="20"/>
-      <c r="AD80" s="16"/>
-      <c r="AF80" s="17"/>
-      <c r="AG80" s="25"/>
-      <c r="AH80" s="25"/>
-      <c r="AI80" s="26"/>
+      <c r="AE80" s="17"/>
+      <c r="AF80" s="25"/>
+      <c r="AG80" s="16"/>
+      <c r="AH80" s="26"/>
+      <c r="AI80" s="25"/>
       <c r="AJ80" s="16"/>
       <c r="AK80" s="16"/>
       <c r="AL80" s="16"/>
@@ -9250,7 +9250,7 @@
       <c r="BW80" s="20"/>
       <c r="BX80" s="20"/>
       <c r="BY80" s="20"/>
-      <c r="CG80" s="20"/>
+      <c r="CH80" s="20"/>
       <c r="CO80" s="27"/>
       <c r="CP80" s="17"/>
       <c r="CQ80" s="17"/>
@@ -9272,14 +9272,14 @@
       <c r="S81" s="20"/>
       <c r="T81" s="20"/>
       <c r="U81" s="20"/>
-      <c r="X81" s="20"/>
+      <c r="Y81" s="20"/>
       <c r="AB81" s="20"/>
       <c r="AC81" s="20"/>
-      <c r="AD81" s="16"/>
-      <c r="AF81" s="17"/>
-      <c r="AG81" s="25"/>
-      <c r="AH81" s="25"/>
-      <c r="AI81" s="26"/>
+      <c r="AE81" s="17"/>
+      <c r="AF81" s="25"/>
+      <c r="AG81" s="16"/>
+      <c r="AH81" s="26"/>
+      <c r="AI81" s="25"/>
       <c r="AJ81" s="16"/>
       <c r="AK81" s="16"/>
       <c r="AL81" s="16"/>
@@ -9304,7 +9304,7 @@
       <c r="BW81" s="20"/>
       <c r="BX81" s="20"/>
       <c r="BY81" s="20"/>
-      <c r="CG81" s="20"/>
+      <c r="CH81" s="20"/>
       <c r="CO81" s="27"/>
       <c r="CP81" s="17"/>
       <c r="CQ81" s="17"/>
@@ -9326,14 +9326,14 @@
       <c r="S82" s="20"/>
       <c r="T82" s="20"/>
       <c r="U82" s="20"/>
-      <c r="X82" s="20"/>
+      <c r="Y82" s="20"/>
       <c r="AB82" s="20"/>
       <c r="AC82" s="20"/>
-      <c r="AD82" s="16"/>
-      <c r="AF82" s="17"/>
-      <c r="AG82" s="25"/>
-      <c r="AH82" s="25"/>
-      <c r="AI82" s="26"/>
+      <c r="AE82" s="17"/>
+      <c r="AF82" s="25"/>
+      <c r="AG82" s="16"/>
+      <c r="AH82" s="26"/>
+      <c r="AI82" s="25"/>
       <c r="AJ82" s="16"/>
       <c r="AK82" s="16"/>
       <c r="AL82" s="16"/>
@@ -9358,7 +9358,7 @@
       <c r="BW82" s="20"/>
       <c r="BX82" s="20"/>
       <c r="BY82" s="20"/>
-      <c r="CG82" s="20"/>
+      <c r="CH82" s="20"/>
       <c r="CO82" s="27"/>
       <c r="CP82" s="17"/>
       <c r="CQ82" s="17"/>
@@ -9380,14 +9380,14 @@
       <c r="S83" s="20"/>
       <c r="T83" s="20"/>
       <c r="U83" s="20"/>
-      <c r="X83" s="20"/>
+      <c r="Y83" s="20"/>
       <c r="AB83" s="20"/>
       <c r="AC83" s="20"/>
-      <c r="AD83" s="16"/>
-      <c r="AF83" s="17"/>
-      <c r="AG83" s="25"/>
-      <c r="AH83" s="25"/>
-      <c r="AI83" s="26"/>
+      <c r="AE83" s="17"/>
+      <c r="AF83" s="25"/>
+      <c r="AG83" s="16"/>
+      <c r="AH83" s="26"/>
+      <c r="AI83" s="25"/>
       <c r="AJ83" s="16"/>
       <c r="AK83" s="16"/>
       <c r="AL83" s="16"/>
@@ -9412,7 +9412,7 @@
       <c r="BW83" s="20"/>
       <c r="BX83" s="20"/>
       <c r="BY83" s="20"/>
-      <c r="CG83" s="20"/>
+      <c r="CH83" s="20"/>
       <c r="CO83" s="27"/>
       <c r="CP83" s="17"/>
       <c r="CQ83" s="17"/>
@@ -9434,14 +9434,14 @@
       <c r="S84" s="20"/>
       <c r="T84" s="20"/>
       <c r="U84" s="20"/>
-      <c r="X84" s="20"/>
+      <c r="Y84" s="20"/>
       <c r="AB84" s="20"/>
       <c r="AC84" s="20"/>
-      <c r="AD84" s="16"/>
-      <c r="AF84" s="17"/>
-      <c r="AG84" s="25"/>
-      <c r="AH84" s="25"/>
-      <c r="AI84" s="26"/>
+      <c r="AE84" s="17"/>
+      <c r="AF84" s="25"/>
+      <c r="AG84" s="16"/>
+      <c r="AH84" s="26"/>
+      <c r="AI84" s="25"/>
       <c r="AJ84" s="16"/>
       <c r="AK84" s="16"/>
       <c r="AL84" s="16"/>
@@ -9466,7 +9466,7 @@
       <c r="BW84" s="20"/>
       <c r="BX84" s="20"/>
       <c r="BY84" s="20"/>
-      <c r="CG84" s="20"/>
+      <c r="CH84" s="20"/>
       <c r="CO84" s="27"/>
       <c r="CP84" s="17"/>
       <c r="CQ84" s="17"/>
@@ -9488,14 +9488,14 @@
       <c r="S85" s="20"/>
       <c r="T85" s="20"/>
       <c r="U85" s="20"/>
-      <c r="X85" s="20"/>
+      <c r="Y85" s="20"/>
       <c r="AB85" s="20"/>
       <c r="AC85" s="20"/>
-      <c r="AD85" s="16"/>
-      <c r="AF85" s="17"/>
-      <c r="AG85" s="25"/>
-      <c r="AH85" s="25"/>
-      <c r="AI85" s="26"/>
+      <c r="AE85" s="17"/>
+      <c r="AF85" s="25"/>
+      <c r="AG85" s="16"/>
+      <c r="AH85" s="26"/>
+      <c r="AI85" s="25"/>
       <c r="AJ85" s="16"/>
       <c r="AK85" s="16"/>
       <c r="AL85" s="16"/>
@@ -9520,7 +9520,7 @@
       <c r="BW85" s="20"/>
       <c r="BX85" s="20"/>
       <c r="BY85" s="20"/>
-      <c r="CG85" s="20"/>
+      <c r="CH85" s="20"/>
       <c r="CO85" s="27"/>
       <c r="CP85" s="17"/>
       <c r="CQ85" s="17"/>
@@ -9542,14 +9542,14 @@
       <c r="S86" s="20"/>
       <c r="T86" s="20"/>
       <c r="U86" s="20"/>
-      <c r="X86" s="20"/>
+      <c r="Y86" s="20"/>
       <c r="AB86" s="20"/>
       <c r="AC86" s="20"/>
-      <c r="AD86" s="16"/>
-      <c r="AF86" s="17"/>
-      <c r="AG86" s="25"/>
-      <c r="AH86" s="25"/>
-      <c r="AI86" s="26"/>
+      <c r="AE86" s="17"/>
+      <c r="AF86" s="25"/>
+      <c r="AG86" s="16"/>
+      <c r="AH86" s="26"/>
+      <c r="AI86" s="25"/>
       <c r="AJ86" s="16"/>
       <c r="AK86" s="16"/>
       <c r="AL86" s="16"/>
@@ -9574,7 +9574,7 @@
       <c r="BW86" s="20"/>
       <c r="BX86" s="20"/>
       <c r="BY86" s="20"/>
-      <c r="CG86" s="20"/>
+      <c r="CH86" s="20"/>
       <c r="CO86" s="27"/>
       <c r="CP86" s="17"/>
       <c r="CQ86" s="17"/>
@@ -9596,14 +9596,14 @@
       <c r="S87" s="20"/>
       <c r="T87" s="20"/>
       <c r="U87" s="20"/>
-      <c r="X87" s="20"/>
+      <c r="Y87" s="20"/>
       <c r="AB87" s="20"/>
       <c r="AC87" s="20"/>
-      <c r="AD87" s="16"/>
-      <c r="AF87" s="17"/>
-      <c r="AG87" s="25"/>
-      <c r="AH87" s="25"/>
-      <c r="AI87" s="26"/>
+      <c r="AE87" s="17"/>
+      <c r="AF87" s="25"/>
+      <c r="AG87" s="16"/>
+      <c r="AH87" s="26"/>
+      <c r="AI87" s="25"/>
       <c r="AJ87" s="16"/>
       <c r="AK87" s="16"/>
       <c r="AL87" s="16"/>
@@ -9628,7 +9628,7 @@
       <c r="BW87" s="20"/>
       <c r="BX87" s="20"/>
       <c r="BY87" s="20"/>
-      <c r="CG87" s="20"/>
+      <c r="CH87" s="20"/>
       <c r="CO87" s="27"/>
       <c r="CP87" s="17"/>
       <c r="CQ87" s="17"/>
@@ -9650,14 +9650,14 @@
       <c r="S88" s="20"/>
       <c r="T88" s="20"/>
       <c r="U88" s="20"/>
-      <c r="X88" s="20"/>
+      <c r="Y88" s="20"/>
       <c r="AB88" s="20"/>
       <c r="AC88" s="20"/>
-      <c r="AD88" s="16"/>
-      <c r="AF88" s="17"/>
-      <c r="AG88" s="25"/>
-      <c r="AH88" s="25"/>
-      <c r="AI88" s="26"/>
+      <c r="AE88" s="17"/>
+      <c r="AF88" s="25"/>
+      <c r="AG88" s="16"/>
+      <c r="AH88" s="26"/>
+      <c r="AI88" s="25"/>
       <c r="AJ88" s="16"/>
       <c r="AK88" s="16"/>
       <c r="AL88" s="16"/>
@@ -9682,7 +9682,7 @@
       <c r="BW88" s="20"/>
       <c r="BX88" s="20"/>
       <c r="BY88" s="20"/>
-      <c r="CG88" s="20"/>
+      <c r="CH88" s="20"/>
       <c r="CO88" s="27"/>
       <c r="CP88" s="17"/>
       <c r="CQ88" s="17"/>
@@ -9704,14 +9704,14 @@
       <c r="S89" s="20"/>
       <c r="T89" s="20"/>
       <c r="U89" s="20"/>
-      <c r="X89" s="20"/>
+      <c r="Y89" s="20"/>
       <c r="AB89" s="20"/>
       <c r="AC89" s="20"/>
-      <c r="AD89" s="16"/>
-      <c r="AF89" s="17"/>
-      <c r="AG89" s="25"/>
-      <c r="AH89" s="25"/>
-      <c r="AI89" s="26"/>
+      <c r="AE89" s="17"/>
+      <c r="AF89" s="25"/>
+      <c r="AG89" s="16"/>
+      <c r="AH89" s="26"/>
+      <c r="AI89" s="25"/>
       <c r="AJ89" s="16"/>
       <c r="AK89" s="16"/>
       <c r="AL89" s="16"/>
@@ -9736,7 +9736,7 @@
       <c r="BW89" s="20"/>
       <c r="BX89" s="20"/>
       <c r="BY89" s="20"/>
-      <c r="CG89" s="20"/>
+      <c r="CH89" s="20"/>
       <c r="CO89" s="27"/>
       <c r="CP89" s="17"/>
       <c r="CQ89" s="17"/>
@@ -9758,14 +9758,14 @@
       <c r="S90" s="20"/>
       <c r="T90" s="20"/>
       <c r="U90" s="20"/>
-      <c r="X90" s="20"/>
+      <c r="Y90" s="20"/>
       <c r="AB90" s="20"/>
       <c r="AC90" s="20"/>
-      <c r="AD90" s="16"/>
-      <c r="AF90" s="17"/>
-      <c r="AG90" s="25"/>
-      <c r="AH90" s="25"/>
-      <c r="AI90" s="26"/>
+      <c r="AE90" s="17"/>
+      <c r="AF90" s="25"/>
+      <c r="AG90" s="16"/>
+      <c r="AH90" s="26"/>
+      <c r="AI90" s="25"/>
       <c r="AJ90" s="16"/>
       <c r="AK90" s="16"/>
       <c r="AL90" s="16"/>
@@ -9790,7 +9790,7 @@
       <c r="BW90" s="20"/>
       <c r="BX90" s="20"/>
       <c r="BY90" s="20"/>
-      <c r="CG90" s="20"/>
+      <c r="CH90" s="20"/>
       <c r="CO90" s="27"/>
       <c r="CP90" s="17"/>
       <c r="CQ90" s="17"/>
@@ -9812,14 +9812,14 @@
       <c r="S91" s="20"/>
       <c r="T91" s="20"/>
       <c r="U91" s="20"/>
-      <c r="X91" s="20"/>
+      <c r="Y91" s="20"/>
       <c r="AB91" s="20"/>
       <c r="AC91" s="20"/>
-      <c r="AD91" s="16"/>
-      <c r="AF91" s="17"/>
-      <c r="AG91" s="25"/>
-      <c r="AH91" s="25"/>
-      <c r="AI91" s="26"/>
+      <c r="AE91" s="17"/>
+      <c r="AF91" s="25"/>
+      <c r="AG91" s="16"/>
+      <c r="AH91" s="26"/>
+      <c r="AI91" s="25"/>
       <c r="AJ91" s="16"/>
       <c r="AK91" s="16"/>
       <c r="AL91" s="16"/>
@@ -9844,7 +9844,7 @@
       <c r="BW91" s="20"/>
       <c r="BX91" s="20"/>
       <c r="BY91" s="20"/>
-      <c r="CG91" s="20"/>
+      <c r="CH91" s="20"/>
       <c r="CO91" s="27"/>
       <c r="CP91" s="17"/>
       <c r="CQ91" s="17"/>
@@ -9866,14 +9866,14 @@
       <c r="S92" s="20"/>
       <c r="T92" s="20"/>
       <c r="U92" s="20"/>
-      <c r="X92" s="20"/>
+      <c r="Y92" s="20"/>
       <c r="AB92" s="20"/>
       <c r="AC92" s="20"/>
-      <c r="AD92" s="16"/>
-      <c r="AF92" s="17"/>
-      <c r="AG92" s="25"/>
-      <c r="AH92" s="25"/>
-      <c r="AI92" s="26"/>
+      <c r="AE92" s="17"/>
+      <c r="AF92" s="25"/>
+      <c r="AG92" s="16"/>
+      <c r="AH92" s="26"/>
+      <c r="AI92" s="25"/>
       <c r="AJ92" s="16"/>
       <c r="AK92" s="16"/>
       <c r="AL92" s="16"/>
@@ -9898,7 +9898,7 @@
       <c r="BW92" s="20"/>
       <c r="BX92" s="20"/>
       <c r="BY92" s="20"/>
-      <c r="CG92" s="20"/>
+      <c r="CH92" s="20"/>
       <c r="CO92" s="27"/>
       <c r="CP92" s="17"/>
       <c r="CQ92" s="17"/>
@@ -9920,14 +9920,14 @@
       <c r="S93" s="20"/>
       <c r="T93" s="20"/>
       <c r="U93" s="20"/>
-      <c r="X93" s="20"/>
+      <c r="Y93" s="20"/>
       <c r="AB93" s="20"/>
       <c r="AC93" s="20"/>
-      <c r="AD93" s="16"/>
-      <c r="AF93" s="17"/>
-      <c r="AG93" s="25"/>
-      <c r="AH93" s="25"/>
-      <c r="AI93" s="26"/>
+      <c r="AE93" s="17"/>
+      <c r="AF93" s="25"/>
+      <c r="AG93" s="16"/>
+      <c r="AH93" s="26"/>
+      <c r="AI93" s="25"/>
       <c r="AJ93" s="16"/>
       <c r="AK93" s="16"/>
       <c r="AL93" s="16"/>
@@ -9952,7 +9952,7 @@
       <c r="BW93" s="20"/>
       <c r="BX93" s="20"/>
       <c r="BY93" s="20"/>
-      <c r="CG93" s="20"/>
+      <c r="CH93" s="20"/>
       <c r="CO93" s="27"/>
       <c r="CP93" s="17"/>
       <c r="CQ93" s="17"/>
@@ -9974,14 +9974,14 @@
       <c r="S94" s="20"/>
       <c r="T94" s="20"/>
       <c r="U94" s="20"/>
-      <c r="X94" s="20"/>
+      <c r="Y94" s="20"/>
       <c r="AB94" s="20"/>
       <c r="AC94" s="20"/>
-      <c r="AD94" s="16"/>
-      <c r="AF94" s="17"/>
-      <c r="AG94" s="25"/>
-      <c r="AH94" s="25"/>
-      <c r="AI94" s="26"/>
+      <c r="AE94" s="17"/>
+      <c r="AF94" s="25"/>
+      <c r="AG94" s="16"/>
+      <c r="AH94" s="26"/>
+      <c r="AI94" s="25"/>
       <c r="AJ94" s="16"/>
       <c r="AK94" s="16"/>
       <c r="AL94" s="16"/>
@@ -10006,7 +10006,7 @@
       <c r="BW94" s="20"/>
       <c r="BX94" s="20"/>
       <c r="BY94" s="20"/>
-      <c r="CG94" s="20"/>
+      <c r="CH94" s="20"/>
       <c r="CO94" s="27"/>
       <c r="CP94" s="17"/>
       <c r="CQ94" s="17"/>
@@ -10028,14 +10028,14 @@
       <c r="S95" s="20"/>
       <c r="T95" s="20"/>
       <c r="U95" s="20"/>
-      <c r="X95" s="20"/>
+      <c r="Y95" s="20"/>
       <c r="AB95" s="20"/>
       <c r="AC95" s="20"/>
-      <c r="AD95" s="16"/>
-      <c r="AF95" s="17"/>
-      <c r="AG95" s="25"/>
-      <c r="AH95" s="25"/>
-      <c r="AI95" s="26"/>
+      <c r="AE95" s="17"/>
+      <c r="AF95" s="25"/>
+      <c r="AG95" s="16"/>
+      <c r="AH95" s="26"/>
+      <c r="AI95" s="25"/>
       <c r="AJ95" s="16"/>
       <c r="AK95" s="16"/>
       <c r="AL95" s="16"/>
@@ -10060,7 +10060,7 @@
       <c r="BW95" s="20"/>
       <c r="BX95" s="20"/>
       <c r="BY95" s="20"/>
-      <c r="CG95" s="20"/>
+      <c r="CH95" s="20"/>
       <c r="CO95" s="27"/>
       <c r="CP95" s="17"/>
       <c r="CQ95" s="17"/>
@@ -10082,14 +10082,14 @@
       <c r="S96" s="20"/>
       <c r="T96" s="20"/>
       <c r="U96" s="20"/>
-      <c r="X96" s="20"/>
+      <c r="Y96" s="20"/>
       <c r="AB96" s="20"/>
       <c r="AC96" s="20"/>
-      <c r="AD96" s="16"/>
-      <c r="AF96" s="17"/>
-      <c r="AG96" s="25"/>
-      <c r="AH96" s="25"/>
-      <c r="AI96" s="26"/>
+      <c r="AE96" s="17"/>
+      <c r="AF96" s="25"/>
+      <c r="AG96" s="16"/>
+      <c r="AH96" s="26"/>
+      <c r="AI96" s="25"/>
       <c r="AJ96" s="16"/>
       <c r="AK96" s="16"/>
       <c r="AL96" s="16"/>
@@ -10114,7 +10114,7 @@
       <c r="BW96" s="20"/>
       <c r="BX96" s="20"/>
       <c r="BY96" s="20"/>
-      <c r="CG96" s="20"/>
+      <c r="CH96" s="20"/>
       <c r="CO96" s="27"/>
       <c r="CP96" s="17"/>
       <c r="CQ96" s="17"/>
@@ -10136,14 +10136,14 @@
       <c r="S97" s="20"/>
       <c r="T97" s="20"/>
       <c r="U97" s="20"/>
-      <c r="X97" s="20"/>
+      <c r="Y97" s="20"/>
       <c r="AB97" s="20"/>
       <c r="AC97" s="20"/>
-      <c r="AD97" s="16"/>
-      <c r="AF97" s="17"/>
-      <c r="AG97" s="25"/>
-      <c r="AH97" s="25"/>
-      <c r="AI97" s="26"/>
+      <c r="AE97" s="17"/>
+      <c r="AF97" s="25"/>
+      <c r="AG97" s="16"/>
+      <c r="AH97" s="26"/>
+      <c r="AI97" s="25"/>
       <c r="AJ97" s="16"/>
       <c r="AK97" s="16"/>
       <c r="AL97" s="16"/>
@@ -10168,7 +10168,7 @@
       <c r="BW97" s="20"/>
       <c r="BX97" s="20"/>
       <c r="BY97" s="20"/>
-      <c r="CG97" s="20"/>
+      <c r="CH97" s="20"/>
       <c r="CO97" s="27"/>
       <c r="CP97" s="17"/>
       <c r="CQ97" s="17"/>
@@ -10190,14 +10190,14 @@
       <c r="S98" s="20"/>
       <c r="T98" s="20"/>
       <c r="U98" s="20"/>
-      <c r="X98" s="20"/>
+      <c r="Y98" s="20"/>
       <c r="AB98" s="20"/>
       <c r="AC98" s="20"/>
-      <c r="AD98" s="16"/>
-      <c r="AF98" s="17"/>
-      <c r="AG98" s="25"/>
-      <c r="AH98" s="25"/>
-      <c r="AI98" s="26"/>
+      <c r="AE98" s="17"/>
+      <c r="AF98" s="25"/>
+      <c r="AG98" s="16"/>
+      <c r="AH98" s="26"/>
+      <c r="AI98" s="25"/>
       <c r="AJ98" s="16"/>
       <c r="AK98" s="16"/>
       <c r="AL98" s="16"/>
@@ -10222,7 +10222,7 @@
       <c r="BW98" s="20"/>
       <c r="BX98" s="20"/>
       <c r="BY98" s="20"/>
-      <c r="CG98" s="20"/>
+      <c r="CH98" s="20"/>
       <c r="CO98" s="27"/>
       <c r="CP98" s="17"/>
       <c r="CQ98" s="17"/>
@@ -10244,14 +10244,14 @@
       <c r="S99" s="20"/>
       <c r="T99" s="20"/>
       <c r="U99" s="20"/>
-      <c r="X99" s="20"/>
+      <c r="Y99" s="20"/>
       <c r="AB99" s="20"/>
       <c r="AC99" s="20"/>
-      <c r="AD99" s="16"/>
-      <c r="AF99" s="17"/>
-      <c r="AG99" s="25"/>
-      <c r="AH99" s="25"/>
-      <c r="AI99" s="26"/>
+      <c r="AE99" s="17"/>
+      <c r="AF99" s="25"/>
+      <c r="AG99" s="16"/>
+      <c r="AH99" s="26"/>
+      <c r="AI99" s="25"/>
       <c r="AJ99" s="16"/>
       <c r="AK99" s="16"/>
       <c r="AL99" s="16"/>
@@ -10276,7 +10276,7 @@
       <c r="BW99" s="20"/>
       <c r="BX99" s="20"/>
       <c r="BY99" s="20"/>
-      <c r="CG99" s="20"/>
+      <c r="CH99" s="20"/>
       <c r="CO99" s="27"/>
       <c r="CP99" s="17"/>
       <c r="CQ99" s="17"/>
@@ -10298,14 +10298,14 @@
       <c r="S100" s="20"/>
       <c r="T100" s="20"/>
       <c r="U100" s="20"/>
-      <c r="X100" s="20"/>
+      <c r="Y100" s="20"/>
       <c r="AB100" s="20"/>
       <c r="AC100" s="20"/>
-      <c r="AD100" s="16"/>
-      <c r="AF100" s="17"/>
-      <c r="AG100" s="25"/>
-      <c r="AH100" s="25"/>
-      <c r="AI100" s="26"/>
+      <c r="AE100" s="17"/>
+      <c r="AF100" s="25"/>
+      <c r="AG100" s="16"/>
+      <c r="AH100" s="26"/>
+      <c r="AI100" s="25"/>
       <c r="AJ100" s="16"/>
       <c r="AK100" s="16"/>
       <c r="AL100" s="16"/>
@@ -10330,7 +10330,7 @@
       <c r="BW100" s="20"/>
       <c r="BX100" s="20"/>
       <c r="BY100" s="20"/>
-      <c r="CG100" s="20"/>
+      <c r="CH100" s="20"/>
       <c r="CO100" s="27"/>
       <c r="CP100" s="17"/>
       <c r="CQ100" s="17"/>
@@ -10352,14 +10352,14 @@
       <c r="S101" s="20"/>
       <c r="T101" s="20"/>
       <c r="U101" s="20"/>
-      <c r="X101" s="20"/>
+      <c r="Y101" s="20"/>
       <c r="AB101" s="20"/>
       <c r="AC101" s="20"/>
-      <c r="AD101" s="16"/>
-      <c r="AF101" s="17"/>
-      <c r="AG101" s="25"/>
-      <c r="AH101" s="25"/>
-      <c r="AI101" s="26"/>
+      <c r="AE101" s="17"/>
+      <c r="AF101" s="25"/>
+      <c r="AG101" s="16"/>
+      <c r="AH101" s="26"/>
+      <c r="AI101" s="25"/>
       <c r="AJ101" s="16"/>
       <c r="AK101" s="16"/>
       <c r="AL101" s="16"/>
@@ -10384,7 +10384,7 @@
       <c r="BW101" s="20"/>
       <c r="BX101" s="20"/>
       <c r="BY101" s="20"/>
-      <c r="CG101" s="20"/>
+      <c r="CH101" s="20"/>
       <c r="CO101" s="27"/>
       <c r="CP101" s="17"/>
       <c r="CQ101" s="17"/>
@@ -10406,14 +10406,14 @@
       <c r="S102" s="20"/>
       <c r="T102" s="20"/>
       <c r="U102" s="20"/>
-      <c r="X102" s="20"/>
+      <c r="Y102" s="20"/>
       <c r="AB102" s="20"/>
       <c r="AC102" s="20"/>
-      <c r="AD102" s="16"/>
-      <c r="AF102" s="17"/>
-      <c r="AG102" s="25"/>
-      <c r="AH102" s="25"/>
-      <c r="AI102" s="26"/>
+      <c r="AE102" s="17"/>
+      <c r="AF102" s="25"/>
+      <c r="AG102" s="16"/>
+      <c r="AH102" s="26"/>
+      <c r="AI102" s="25"/>
       <c r="AJ102" s="16"/>
       <c r="AK102" s="16"/>
       <c r="AL102" s="16"/>
@@ -10438,7 +10438,7 @@
       <c r="BW102" s="20"/>
       <c r="BX102" s="20"/>
       <c r="BY102" s="20"/>
-      <c r="CG102" s="20"/>
+      <c r="CH102" s="20"/>
       <c r="CO102" s="27"/>
       <c r="CP102" s="17"/>
       <c r="CQ102" s="17"/>
@@ -10460,14 +10460,14 @@
       <c r="S103" s="20"/>
       <c r="T103" s="20"/>
       <c r="U103" s="20"/>
-      <c r="X103" s="20"/>
+      <c r="Y103" s="20"/>
       <c r="AB103" s="20"/>
       <c r="AC103" s="20"/>
-      <c r="AD103" s="16"/>
-      <c r="AF103" s="17"/>
-      <c r="AG103" s="25"/>
-      <c r="AH103" s="25"/>
-      <c r="AI103" s="26"/>
+      <c r="AE103" s="17"/>
+      <c r="AF103" s="25"/>
+      <c r="AG103" s="16"/>
+      <c r="AH103" s="26"/>
+      <c r="AI103" s="25"/>
       <c r="AJ103" s="16"/>
       <c r="AK103" s="16"/>
       <c r="AL103" s="16"/>
@@ -10492,7 +10492,7 @@
       <c r="BW103" s="20"/>
       <c r="BX103" s="20"/>
       <c r="BY103" s="20"/>
-      <c r="CG103" s="20"/>
+      <c r="CH103" s="20"/>
       <c r="CO103" s="27"/>
       <c r="CP103" s="17"/>
       <c r="CQ103" s="17"/>
@@ -10514,14 +10514,14 @@
       <c r="S104" s="20"/>
       <c r="T104" s="20"/>
       <c r="U104" s="20"/>
-      <c r="X104" s="20"/>
+      <c r="Y104" s="20"/>
       <c r="AB104" s="20"/>
       <c r="AC104" s="20"/>
-      <c r="AD104" s="16"/>
-      <c r="AF104" s="17"/>
-      <c r="AG104" s="25"/>
-      <c r="AH104" s="25"/>
-      <c r="AI104" s="26"/>
+      <c r="AE104" s="17"/>
+      <c r="AF104" s="25"/>
+      <c r="AG104" s="16"/>
+      <c r="AH104" s="26"/>
+      <c r="AI104" s="25"/>
       <c r="AJ104" s="16"/>
       <c r="AK104" s="16"/>
       <c r="AL104" s="16"/>
@@ -10546,7 +10546,7 @@
       <c r="BW104" s="20"/>
       <c r="BX104" s="20"/>
       <c r="BY104" s="20"/>
-      <c r="CG104" s="20"/>
+      <c r="CH104" s="20"/>
       <c r="CO104" s="27"/>
       <c r="CP104" s="17"/>
       <c r="CQ104" s="17"/>
@@ -10568,14 +10568,14 @@
       <c r="S105" s="20"/>
       <c r="T105" s="20"/>
       <c r="U105" s="20"/>
-      <c r="X105" s="20"/>
+      <c r="Y105" s="20"/>
       <c r="AB105" s="20"/>
       <c r="AC105" s="20"/>
-      <c r="AD105" s="16"/>
-      <c r="AF105" s="17"/>
-      <c r="AG105" s="25"/>
-      <c r="AH105" s="25"/>
-      <c r="AI105" s="26"/>
+      <c r="AE105" s="17"/>
+      <c r="AF105" s="25"/>
+      <c r="AG105" s="16"/>
+      <c r="AH105" s="26"/>
+      <c r="AI105" s="25"/>
       <c r="AJ105" s="16"/>
       <c r="AK105" s="16"/>
       <c r="AL105" s="16"/>
@@ -10600,7 +10600,7 @@
       <c r="BW105" s="20"/>
       <c r="BX105" s="20"/>
       <c r="BY105" s="20"/>
-      <c r="CG105" s="20"/>
+      <c r="CH105" s="20"/>
       <c r="CO105" s="27"/>
       <c r="CP105" s="17"/>
       <c r="CQ105" s="17"/>
@@ -10622,14 +10622,14 @@
       <c r="S106" s="20"/>
       <c r="T106" s="20"/>
       <c r="U106" s="20"/>
-      <c r="X106" s="20"/>
+      <c r="Y106" s="20"/>
       <c r="AB106" s="20"/>
       <c r="AC106" s="20"/>
-      <c r="AD106" s="16"/>
-      <c r="AF106" s="17"/>
-      <c r="AG106" s="25"/>
-      <c r="AH106" s="25"/>
-      <c r="AI106" s="26"/>
+      <c r="AE106" s="17"/>
+      <c r="AF106" s="25"/>
+      <c r="AG106" s="16"/>
+      <c r="AH106" s="26"/>
+      <c r="AI106" s="25"/>
       <c r="AJ106" s="16"/>
       <c r="AK106" s="16"/>
       <c r="AL106" s="16"/>
@@ -10654,7 +10654,7 @@
       <c r="BW106" s="20"/>
       <c r="BX106" s="20"/>
       <c r="BY106" s="20"/>
-      <c r="CG106" s="20"/>
+      <c r="CH106" s="20"/>
       <c r="CO106" s="27"/>
       <c r="CP106" s="17"/>
       <c r="CQ106" s="17"/>
@@ -10676,14 +10676,14 @@
       <c r="S107" s="20"/>
       <c r="T107" s="20"/>
       <c r="U107" s="20"/>
-      <c r="X107" s="20"/>
+      <c r="Y107" s="20"/>
       <c r="AB107" s="20"/>
       <c r="AC107" s="20"/>
-      <c r="AD107" s="16"/>
-      <c r="AF107" s="17"/>
-      <c r="AG107" s="25"/>
-      <c r="AH107" s="25"/>
-      <c r="AI107" s="26"/>
+      <c r="AE107" s="17"/>
+      <c r="AF107" s="25"/>
+      <c r="AG107" s="16"/>
+      <c r="AH107" s="26"/>
+      <c r="AI107" s="25"/>
       <c r="AJ107" s="16"/>
       <c r="AK107" s="16"/>
       <c r="AL107" s="16"/>
@@ -10708,7 +10708,7 @@
       <c r="BW107" s="20"/>
       <c r="BX107" s="20"/>
       <c r="BY107" s="20"/>
-      <c r="CG107" s="20"/>
+      <c r="CH107" s="20"/>
       <c r="CO107" s="27"/>
       <c r="CP107" s="17"/>
       <c r="CQ107" s="17"/>
@@ -10730,14 +10730,14 @@
       <c r="S108" s="20"/>
       <c r="T108" s="20"/>
       <c r="U108" s="20"/>
-      <c r="X108" s="20"/>
+      <c r="Y108" s="20"/>
       <c r="AB108" s="20"/>
       <c r="AC108" s="20"/>
-      <c r="AD108" s="16"/>
-      <c r="AF108" s="17"/>
-      <c r="AG108" s="25"/>
-      <c r="AH108" s="25"/>
-      <c r="AI108" s="26"/>
+      <c r="AE108" s="17"/>
+      <c r="AF108" s="25"/>
+      <c r="AG108" s="16"/>
+      <c r="AH108" s="26"/>
+      <c r="AI108" s="25"/>
       <c r="AJ108" s="16"/>
       <c r="AK108" s="16"/>
       <c r="AL108" s="16"/>
@@ -10762,7 +10762,7 @@
       <c r="BW108" s="20"/>
       <c r="BX108" s="20"/>
       <c r="BY108" s="20"/>
-      <c r="CG108" s="20"/>
+      <c r="CH108" s="20"/>
       <c r="CO108" s="27"/>
       <c r="CP108" s="17"/>
       <c r="CQ108" s="17"/>
@@ -10784,14 +10784,14 @@
       <c r="S109" s="20"/>
       <c r="T109" s="20"/>
       <c r="U109" s="20"/>
-      <c r="X109" s="20"/>
+      <c r="Y109" s="20"/>
       <c r="AB109" s="20"/>
       <c r="AC109" s="20"/>
-      <c r="AD109" s="16"/>
-      <c r="AF109" s="17"/>
-      <c r="AG109" s="25"/>
-      <c r="AH109" s="25"/>
-      <c r="AI109" s="26"/>
+      <c r="AE109" s="17"/>
+      <c r="AF109" s="25"/>
+      <c r="AG109" s="16"/>
+      <c r="AH109" s="26"/>
+      <c r="AI109" s="25"/>
       <c r="AJ109" s="16"/>
       <c r="AK109" s="16"/>
       <c r="AL109" s="16"/>
@@ -10816,7 +10816,7 @@
       <c r="BW109" s="20"/>
       <c r="BX109" s="20"/>
       <c r="BY109" s="20"/>
-      <c r="CG109" s="20"/>
+      <c r="CH109" s="20"/>
       <c r="CO109" s="27"/>
       <c r="CP109" s="17"/>
       <c r="CQ109" s="17"/>
@@ -10838,14 +10838,14 @@
       <c r="S110" s="20"/>
       <c r="T110" s="20"/>
       <c r="U110" s="20"/>
-      <c r="X110" s="20"/>
+      <c r="Y110" s="20"/>
       <c r="AB110" s="20"/>
       <c r="AC110" s="20"/>
-      <c r="AD110" s="16"/>
-      <c r="AF110" s="17"/>
-      <c r="AG110" s="25"/>
-      <c r="AH110" s="25"/>
-      <c r="AI110" s="26"/>
+      <c r="AE110" s="17"/>
+      <c r="AF110" s="25"/>
+      <c r="AG110" s="16"/>
+      <c r="AH110" s="26"/>
+      <c r="AI110" s="25"/>
       <c r="AJ110" s="16"/>
       <c r="AK110" s="16"/>
       <c r="AL110" s="16"/>
@@ -10870,7 +10870,7 @@
       <c r="BW110" s="20"/>
       <c r="BX110" s="20"/>
       <c r="BY110" s="20"/>
-      <c r="CG110" s="20"/>
+      <c r="CH110" s="20"/>
       <c r="CO110" s="27"/>
       <c r="CP110" s="17"/>
       <c r="CQ110" s="17"/>
@@ -10892,14 +10892,14 @@
       <c r="S111" s="20"/>
       <c r="T111" s="20"/>
       <c r="U111" s="20"/>
-      <c r="X111" s="20"/>
+      <c r="Y111" s="20"/>
       <c r="AB111" s="20"/>
       <c r="AC111" s="20"/>
-      <c r="AD111" s="16"/>
-      <c r="AF111" s="17"/>
-      <c r="AG111" s="25"/>
-      <c r="AH111" s="25"/>
-      <c r="AI111" s="26"/>
+      <c r="AE111" s="17"/>
+      <c r="AF111" s="25"/>
+      <c r="AG111" s="16"/>
+      <c r="AH111" s="26"/>
+      <c r="AI111" s="25"/>
       <c r="AJ111" s="16"/>
       <c r="AK111" s="16"/>
       <c r="AL111" s="16"/>
@@ -10924,7 +10924,7 @@
       <c r="BW111" s="20"/>
       <c r="BX111" s="20"/>
       <c r="BY111" s="20"/>
-      <c r="CG111" s="20"/>
+      <c r="CH111" s="20"/>
       <c r="CO111" s="27"/>
       <c r="CP111" s="17"/>
       <c r="CQ111" s="17"/>
@@ -10946,14 +10946,14 @@
       <c r="S112" s="20"/>
       <c r="T112" s="20"/>
       <c r="U112" s="20"/>
-      <c r="X112" s="20"/>
+      <c r="Y112" s="20"/>
       <c r="AB112" s="20"/>
       <c r="AC112" s="20"/>
-      <c r="AD112" s="16"/>
-      <c r="AF112" s="17"/>
-      <c r="AG112" s="25"/>
-      <c r="AH112" s="25"/>
-      <c r="AI112" s="26"/>
+      <c r="AE112" s="17"/>
+      <c r="AF112" s="25"/>
+      <c r="AG112" s="16"/>
+      <c r="AH112" s="26"/>
+      <c r="AI112" s="25"/>
       <c r="AJ112" s="16"/>
       <c r="AK112" s="16"/>
       <c r="AL112" s="16"/>
@@ -10978,7 +10978,7 @@
       <c r="BW112" s="20"/>
       <c r="BX112" s="20"/>
       <c r="BY112" s="20"/>
-      <c r="CG112" s="20"/>
+      <c r="CH112" s="20"/>
       <c r="CO112" s="27"/>
       <c r="CP112" s="17"/>
       <c r="CQ112" s="17"/>
@@ -11000,14 +11000,14 @@
       <c r="S113" s="20"/>
       <c r="T113" s="20"/>
       <c r="U113" s="20"/>
-      <c r="X113" s="20"/>
+      <c r="Y113" s="20"/>
       <c r="AB113" s="20"/>
       <c r="AC113" s="20"/>
-      <c r="AD113" s="16"/>
-      <c r="AF113" s="17"/>
-      <c r="AG113" s="25"/>
-      <c r="AH113" s="25"/>
-      <c r="AI113" s="26"/>
+      <c r="AE113" s="17"/>
+      <c r="AF113" s="25"/>
+      <c r="AG113" s="16"/>
+      <c r="AH113" s="26"/>
+      <c r="AI113" s="25"/>
       <c r="AJ113" s="16"/>
       <c r="AK113" s="16"/>
       <c r="AL113" s="16"/>
@@ -11032,7 +11032,7 @@
       <c r="BW113" s="20"/>
       <c r="BX113" s="20"/>
       <c r="BY113" s="20"/>
-      <c r="CG113" s="20"/>
+      <c r="CH113" s="20"/>
       <c r="CO113" s="27"/>
       <c r="CP113" s="17"/>
       <c r="CQ113" s="17"/>
@@ -11054,14 +11054,14 @@
       <c r="S114" s="20"/>
       <c r="T114" s="20"/>
       <c r="U114" s="20"/>
-      <c r="X114" s="20"/>
+      <c r="Y114" s="20"/>
       <c r="AB114" s="20"/>
       <c r="AC114" s="20"/>
-      <c r="AD114" s="16"/>
-      <c r="AF114" s="17"/>
-      <c r="AG114" s="25"/>
-      <c r="AH114" s="25"/>
-      <c r="AI114" s="26"/>
+      <c r="AE114" s="17"/>
+      <c r="AF114" s="25"/>
+      <c r="AG114" s="16"/>
+      <c r="AH114" s="26"/>
+      <c r="AI114" s="25"/>
       <c r="AJ114" s="16"/>
       <c r="AK114" s="16"/>
       <c r="AL114" s="16"/>
@@ -11086,7 +11086,7 @@
       <c r="BW114" s="20"/>
       <c r="BX114" s="20"/>
       <c r="BY114" s="20"/>
-      <c r="CG114" s="20"/>
+      <c r="CH114" s="20"/>
       <c r="CO114" s="27"/>
       <c r="CP114" s="17"/>
       <c r="CQ114" s="17"/>
@@ -11108,14 +11108,14 @@
       <c r="S115" s="20"/>
       <c r="T115" s="20"/>
       <c r="U115" s="20"/>
-      <c r="X115" s="20"/>
+      <c r="Y115" s="20"/>
       <c r="AB115" s="20"/>
       <c r="AC115" s="20"/>
-      <c r="AD115" s="16"/>
-      <c r="AF115" s="17"/>
-      <c r="AG115" s="25"/>
-      <c r="AH115" s="25"/>
-      <c r="AI115" s="26"/>
+      <c r="AE115" s="17"/>
+      <c r="AF115" s="25"/>
+      <c r="AG115" s="16"/>
+      <c r="AH115" s="26"/>
+      <c r="AI115" s="25"/>
       <c r="AJ115" s="16"/>
       <c r="AK115" s="16"/>
       <c r="AL115" s="16"/>
@@ -11140,7 +11140,7 @@
       <c r="BW115" s="20"/>
       <c r="BX115" s="20"/>
       <c r="BY115" s="20"/>
-      <c r="CG115" s="20"/>
+      <c r="CH115" s="20"/>
       <c r="CO115" s="27"/>
       <c r="CP115" s="17"/>
       <c r="CQ115" s="17"/>
@@ -11162,14 +11162,14 @@
       <c r="S116" s="20"/>
       <c r="T116" s="20"/>
       <c r="U116" s="20"/>
-      <c r="X116" s="20"/>
+      <c r="Y116" s="20"/>
       <c r="AB116" s="20"/>
       <c r="AC116" s="20"/>
-      <c r="AD116" s="16"/>
-      <c r="AF116" s="17"/>
-      <c r="AG116" s="25"/>
-      <c r="AH116" s="25"/>
-      <c r="AI116" s="26"/>
+      <c r="AE116" s="17"/>
+      <c r="AF116" s="25"/>
+      <c r="AG116" s="16"/>
+      <c r="AH116" s="26"/>
+      <c r="AI116" s="25"/>
       <c r="AJ116" s="16"/>
       <c r="AK116" s="16"/>
       <c r="AL116" s="16"/>
@@ -11194,7 +11194,7 @@
       <c r="BW116" s="20"/>
       <c r="BX116" s="20"/>
       <c r="BY116" s="20"/>
-      <c r="CG116" s="20"/>
+      <c r="CH116" s="20"/>
       <c r="CO116" s="27"/>
       <c r="CP116" s="17"/>
       <c r="CQ116" s="17"/>
@@ -11216,14 +11216,14 @@
       <c r="S117" s="20"/>
       <c r="T117" s="20"/>
       <c r="U117" s="20"/>
-      <c r="X117" s="20"/>
+      <c r="Y117" s="20"/>
       <c r="AB117" s="20"/>
       <c r="AC117" s="20"/>
-      <c r="AD117" s="16"/>
-      <c r="AF117" s="17"/>
-      <c r="AG117" s="25"/>
-      <c r="AH117" s="25"/>
-      <c r="AI117" s="26"/>
+      <c r="AE117" s="17"/>
+      <c r="AF117" s="25"/>
+      <c r="AG117" s="16"/>
+      <c r="AH117" s="26"/>
+      <c r="AI117" s="25"/>
       <c r="AJ117" s="16"/>
       <c r="AK117" s="16"/>
       <c r="AL117" s="16"/>
@@ -11248,7 +11248,7 @@
       <c r="BW117" s="20"/>
       <c r="BX117" s="20"/>
       <c r="BY117" s="20"/>
-      <c r="CG117" s="20"/>
+      <c r="CH117" s="20"/>
       <c r="CO117" s="27"/>
       <c r="CP117" s="17"/>
       <c r="CQ117" s="17"/>
@@ -11270,14 +11270,14 @@
       <c r="S118" s="20"/>
       <c r="T118" s="20"/>
       <c r="U118" s="20"/>
-      <c r="X118" s="20"/>
+      <c r="Y118" s="20"/>
       <c r="AB118" s="20"/>
       <c r="AC118" s="20"/>
-      <c r="AD118" s="16"/>
-      <c r="AF118" s="17"/>
-      <c r="AG118" s="25"/>
-      <c r="AH118" s="25"/>
-      <c r="AI118" s="26"/>
+      <c r="AE118" s="17"/>
+      <c r="AF118" s="25"/>
+      <c r="AG118" s="16"/>
+      <c r="AH118" s="26"/>
+      <c r="AI118" s="25"/>
       <c r="AJ118" s="16"/>
       <c r="AK118" s="16"/>
       <c r="AL118" s="16"/>
@@ -11302,7 +11302,7 @@
       <c r="BW118" s="20"/>
       <c r="BX118" s="20"/>
       <c r="BY118" s="20"/>
-      <c r="CG118" s="20"/>
+      <c r="CH118" s="20"/>
       <c r="CO118" s="27"/>
       <c r="CP118" s="17"/>
       <c r="CQ118" s="17"/>
@@ -11324,14 +11324,14 @@
       <c r="S119" s="20"/>
       <c r="T119" s="20"/>
       <c r="U119" s="20"/>
-      <c r="X119" s="20"/>
+      <c r="Y119" s="20"/>
       <c r="AB119" s="20"/>
       <c r="AC119" s="20"/>
-      <c r="AD119" s="16"/>
-      <c r="AF119" s="17"/>
-      <c r="AG119" s="25"/>
-      <c r="AH119" s="25"/>
-      <c r="AI119" s="26"/>
+      <c r="AE119" s="17"/>
+      <c r="AF119" s="25"/>
+      <c r="AG119" s="16"/>
+      <c r="AH119" s="26"/>
+      <c r="AI119" s="25"/>
       <c r="AJ119" s="16"/>
       <c r="AK119" s="16"/>
       <c r="AL119" s="16"/>
@@ -11356,7 +11356,7 @@
       <c r="BW119" s="20"/>
       <c r="BX119" s="20"/>
       <c r="BY119" s="20"/>
-      <c r="CG119" s="20"/>
+      <c r="CH119" s="20"/>
       <c r="CO119" s="27"/>
       <c r="CP119" s="17"/>
       <c r="CQ119" s="17"/>
@@ -11378,14 +11378,14 @@
       <c r="S120" s="20"/>
       <c r="T120" s="20"/>
       <c r="U120" s="20"/>
-      <c r="X120" s="20"/>
+      <c r="Y120" s="20"/>
       <c r="AB120" s="20"/>
       <c r="AC120" s="20"/>
-      <c r="AD120" s="16"/>
-      <c r="AF120" s="17"/>
-      <c r="AG120" s="25"/>
-      <c r="AH120" s="25"/>
-      <c r="AI120" s="26"/>
+      <c r="AE120" s="17"/>
+      <c r="AF120" s="25"/>
+      <c r="AG120" s="16"/>
+      <c r="AH120" s="26"/>
+      <c r="AI120" s="25"/>
       <c r="AJ120" s="16"/>
       <c r="AK120" s="16"/>
       <c r="AL120" s="16"/>
@@ -11410,7 +11410,7 @@
       <c r="BW120" s="20"/>
       <c r="BX120" s="20"/>
       <c r="BY120" s="20"/>
-      <c r="CG120" s="20"/>
+      <c r="CH120" s="20"/>
       <c r="CO120" s="27"/>
       <c r="CP120" s="17"/>
       <c r="CQ120" s="17"/>
@@ -11432,14 +11432,14 @@
       <c r="S121" s="20"/>
       <c r="T121" s="20"/>
       <c r="U121" s="20"/>
-      <c r="X121" s="20"/>
+      <c r="Y121" s="20"/>
       <c r="AB121" s="20"/>
       <c r="AC121" s="20"/>
-      <c r="AD121" s="16"/>
-      <c r="AF121" s="17"/>
-      <c r="AG121" s="25"/>
-      <c r="AH121" s="25"/>
-      <c r="AI121" s="26"/>
+      <c r="AE121" s="17"/>
+      <c r="AF121" s="25"/>
+      <c r="AG121" s="16"/>
+      <c r="AH121" s="26"/>
+      <c r="AI121" s="25"/>
       <c r="AJ121" s="16"/>
       <c r="AK121" s="16"/>
       <c r="AL121" s="16"/>
@@ -11464,7 +11464,7 @@
       <c r="BW121" s="20"/>
       <c r="BX121" s="20"/>
       <c r="BY121" s="20"/>
-      <c r="CG121" s="20"/>
+      <c r="CH121" s="20"/>
       <c r="CO121" s="27"/>
       <c r="CP121" s="17"/>
       <c r="CQ121" s="17"/>
@@ -11486,14 +11486,14 @@
       <c r="S122" s="20"/>
       <c r="T122" s="20"/>
       <c r="U122" s="20"/>
-      <c r="X122" s="20"/>
+      <c r="Y122" s="20"/>
       <c r="AB122" s="20"/>
       <c r="AC122" s="20"/>
-      <c r="AD122" s="16"/>
-      <c r="AF122" s="17"/>
-      <c r="AG122" s="25"/>
-      <c r="AH122" s="25"/>
-      <c r="AI122" s="26"/>
+      <c r="AE122" s="17"/>
+      <c r="AF122" s="25"/>
+      <c r="AG122" s="16"/>
+      <c r="AH122" s="26"/>
+      <c r="AI122" s="25"/>
       <c r="AJ122" s="16"/>
       <c r="AK122" s="16"/>
       <c r="AL122" s="16"/>
@@ -11518,7 +11518,7 @@
       <c r="BW122" s="20"/>
       <c r="BX122" s="20"/>
       <c r="BY122" s="20"/>
-      <c r="CG122" s="20"/>
+      <c r="CH122" s="20"/>
       <c r="CO122" s="27"/>
       <c r="CP122" s="17"/>
       <c r="CQ122" s="17"/>
@@ -11540,14 +11540,14 @@
       <c r="S123" s="20"/>
       <c r="T123" s="20"/>
       <c r="U123" s="20"/>
-      <c r="X123" s="20"/>
+      <c r="Y123" s="20"/>
       <c r="AB123" s="20"/>
       <c r="AC123" s="20"/>
-      <c r="AD123" s="16"/>
-      <c r="AF123" s="17"/>
-      <c r="AG123" s="25"/>
-      <c r="AH123" s="25"/>
-      <c r="AI123" s="26"/>
+      <c r="AE123" s="17"/>
+      <c r="AF123" s="25"/>
+      <c r="AG123" s="16"/>
+      <c r="AH123" s="26"/>
+      <c r="AI123" s="25"/>
       <c r="AJ123" s="16"/>
       <c r="AK123" s="16"/>
       <c r="AL123" s="16"/>
@@ -11572,7 +11572,7 @@
       <c r="BW123" s="20"/>
       <c r="BX123" s="20"/>
       <c r="BY123" s="20"/>
-      <c r="CG123" s="20"/>
+      <c r="CH123" s="20"/>
       <c r="CO123" s="27"/>
       <c r="CP123" s="17"/>
       <c r="CQ123" s="17"/>
@@ -11594,14 +11594,14 @@
       <c r="S124" s="20"/>
       <c r="T124" s="20"/>
       <c r="U124" s="20"/>
-      <c r="X124" s="20"/>
+      <c r="Y124" s="20"/>
       <c r="AB124" s="20"/>
       <c r="AC124" s="20"/>
-      <c r="AD124" s="16"/>
-      <c r="AF124" s="17"/>
-      <c r="AG124" s="25"/>
-      <c r="AH124" s="25"/>
-      <c r="AI124" s="26"/>
+      <c r="AE124" s="17"/>
+      <c r="AF124" s="25"/>
+      <c r="AG124" s="16"/>
+      <c r="AH124" s="26"/>
+      <c r="AI124" s="25"/>
       <c r="AJ124" s="16"/>
       <c r="AK124" s="16"/>
       <c r="AL124" s="16"/>
@@ -11626,7 +11626,7 @@
       <c r="BW124" s="20"/>
       <c r="BX124" s="20"/>
       <c r="BY124" s="20"/>
-      <c r="CG124" s="20"/>
+      <c r="CH124" s="20"/>
       <c r="CO124" s="27"/>
       <c r="CP124" s="17"/>
       <c r="CQ124" s="17"/>
@@ -11648,14 +11648,14 @@
       <c r="S125" s="20"/>
       <c r="T125" s="20"/>
       <c r="U125" s="20"/>
-      <c r="X125" s="20"/>
+      <c r="Y125" s="20"/>
       <c r="AB125" s="20"/>
       <c r="AC125" s="20"/>
-      <c r="AD125" s="16"/>
-      <c r="AF125" s="17"/>
-      <c r="AG125" s="25"/>
-      <c r="AH125" s="25"/>
-      <c r="AI125" s="26"/>
+      <c r="AE125" s="17"/>
+      <c r="AF125" s="25"/>
+      <c r="AG125" s="16"/>
+      <c r="AH125" s="26"/>
+      <c r="AI125" s="25"/>
       <c r="AJ125" s="16"/>
       <c r="AK125" s="16"/>
       <c r="AL125" s="16"/>
@@ -11680,7 +11680,7 @@
       <c r="BW125" s="20"/>
       <c r="BX125" s="20"/>
       <c r="BY125" s="20"/>
-      <c r="CG125" s="20"/>
+      <c r="CH125" s="20"/>
       <c r="CO125" s="27"/>
       <c r="CP125" s="17"/>
       <c r="CQ125" s="17"/>
@@ -11702,14 +11702,14 @@
       <c r="S126" s="20"/>
       <c r="T126" s="20"/>
       <c r="U126" s="20"/>
-      <c r="X126" s="20"/>
+      <c r="Y126" s="20"/>
       <c r="AB126" s="20"/>
       <c r="AC126" s="20"/>
-      <c r="AD126" s="16"/>
-      <c r="AF126" s="17"/>
-      <c r="AG126" s="25"/>
-      <c r="AH126" s="25"/>
-      <c r="AI126" s="26"/>
+      <c r="AE126" s="17"/>
+      <c r="AF126" s="25"/>
+      <c r="AG126" s="16"/>
+      <c r="AH126" s="26"/>
+      <c r="AI126" s="25"/>
       <c r="AJ126" s="16"/>
       <c r="AK126" s="16"/>
       <c r="AL126" s="16"/>
@@ -11734,7 +11734,7 @@
       <c r="BW126" s="20"/>
       <c r="BX126" s="20"/>
       <c r="BY126" s="20"/>
-      <c r="CG126" s="20"/>
+      <c r="CH126" s="20"/>
       <c r="CO126" s="27"/>
       <c r="CP126" s="17"/>
       <c r="CQ126" s="17"/>
@@ -11756,14 +11756,14 @@
       <c r="S127" s="20"/>
       <c r="T127" s="20"/>
       <c r="U127" s="20"/>
-      <c r="X127" s="20"/>
+      <c r="Y127" s="20"/>
       <c r="AB127" s="20"/>
       <c r="AC127" s="20"/>
-      <c r="AD127" s="16"/>
-      <c r="AF127" s="17"/>
-      <c r="AG127" s="25"/>
-      <c r="AH127" s="25"/>
-      <c r="AI127" s="26"/>
+      <c r="AE127" s="17"/>
+      <c r="AF127" s="25"/>
+      <c r="AG127" s="16"/>
+      <c r="AH127" s="26"/>
+      <c r="AI127" s="25"/>
       <c r="AJ127" s="16"/>
       <c r="AK127" s="16"/>
       <c r="AL127" s="16"/>
@@ -11788,7 +11788,7 @@
       <c r="BW127" s="20"/>
       <c r="BX127" s="20"/>
       <c r="BY127" s="20"/>
-      <c r="CG127" s="20"/>
+      <c r="CH127" s="20"/>
       <c r="CO127" s="27"/>
       <c r="CP127" s="17"/>
       <c r="CQ127" s="17"/>
@@ -11810,14 +11810,14 @@
       <c r="S128" s="20"/>
       <c r="T128" s="20"/>
       <c r="U128" s="20"/>
-      <c r="X128" s="20"/>
+      <c r="Y128" s="20"/>
       <c r="AB128" s="20"/>
       <c r="AC128" s="20"/>
-      <c r="AD128" s="16"/>
-      <c r="AF128" s="17"/>
-      <c r="AG128" s="25"/>
-      <c r="AH128" s="25"/>
-      <c r="AI128" s="26"/>
+      <c r="AE128" s="17"/>
+      <c r="AF128" s="25"/>
+      <c r="AG128" s="16"/>
+      <c r="AH128" s="26"/>
+      <c r="AI128" s="25"/>
       <c r="AJ128" s="16"/>
       <c r="AK128" s="16"/>
       <c r="AL128" s="16"/>
@@ -11842,7 +11842,7 @@
       <c r="BW128" s="20"/>
       <c r="BX128" s="20"/>
       <c r="BY128" s="20"/>
-      <c r="CG128" s="20"/>
+      <c r="CH128" s="20"/>
       <c r="CO128" s="27"/>
       <c r="CP128" s="17"/>
       <c r="CQ128" s="17"/>
@@ -11864,14 +11864,14 @@
       <c r="S129" s="20"/>
       <c r="T129" s="20"/>
       <c r="U129" s="20"/>
-      <c r="X129" s="20"/>
+      <c r="Y129" s="20"/>
       <c r="AB129" s="20"/>
       <c r="AC129" s="20"/>
-      <c r="AD129" s="16"/>
-      <c r="AF129" s="17"/>
-      <c r="AG129" s="25"/>
-      <c r="AH129" s="25"/>
-      <c r="AI129" s="26"/>
+      <c r="AE129" s="17"/>
+      <c r="AF129" s="25"/>
+      <c r="AG129" s="16"/>
+      <c r="AH129" s="26"/>
+      <c r="AI129" s="25"/>
       <c r="AJ129" s="16"/>
       <c r="AK129" s="16"/>
       <c r="AL129" s="16"/>
@@ -11896,7 +11896,7 @@
       <c r="BW129" s="20"/>
       <c r="BX129" s="20"/>
       <c r="BY129" s="20"/>
-      <c r="CG129" s="20"/>
+      <c r="CH129" s="20"/>
       <c r="CO129" s="27"/>
       <c r="CP129" s="17"/>
       <c r="CQ129" s="17"/>
@@ -11918,14 +11918,14 @@
       <c r="S130" s="20"/>
       <c r="T130" s="20"/>
       <c r="U130" s="20"/>
-      <c r="X130" s="20"/>
+      <c r="Y130" s="20"/>
       <c r="AB130" s="20"/>
       <c r="AC130" s="20"/>
-      <c r="AD130" s="16"/>
-      <c r="AF130" s="17"/>
-      <c r="AG130" s="25"/>
-      <c r="AH130" s="25"/>
-      <c r="AI130" s="26"/>
+      <c r="AE130" s="17"/>
+      <c r="AF130" s="25"/>
+      <c r="AG130" s="16"/>
+      <c r="AH130" s="26"/>
+      <c r="AI130" s="25"/>
       <c r="AJ130" s="16"/>
       <c r="AK130" s="16"/>
       <c r="AL130" s="16"/>
@@ -11950,7 +11950,7 @@
       <c r="BW130" s="20"/>
       <c r="BX130" s="20"/>
       <c r="BY130" s="20"/>
-      <c r="CG130" s="20"/>
+      <c r="CH130" s="20"/>
       <c r="CO130" s="27"/>
       <c r="CP130" s="17"/>
       <c r="CQ130" s="17"/>
@@ -11972,14 +11972,14 @@
       <c r="S131" s="20"/>
       <c r="T131" s="20"/>
       <c r="U131" s="20"/>
-      <c r="X131" s="20"/>
+      <c r="Y131" s="20"/>
       <c r="AB131" s="20"/>
       <c r="AC131" s="20"/>
-      <c r="AD131" s="16"/>
-      <c r="AF131" s="17"/>
-      <c r="AG131" s="25"/>
-      <c r="AH131" s="25"/>
-      <c r="AI131" s="26"/>
+      <c r="AE131" s="17"/>
+      <c r="AF131" s="25"/>
+      <c r="AG131" s="16"/>
+      <c r="AH131" s="26"/>
+      <c r="AI131" s="25"/>
       <c r="AJ131" s="16"/>
       <c r="AK131" s="16"/>
       <c r="AL131" s="16"/>
@@ -12004,7 +12004,7 @@
       <c r="BW131" s="20"/>
       <c r="BX131" s="20"/>
       <c r="BY131" s="20"/>
-      <c r="CG131" s="20"/>
+      <c r="CH131" s="20"/>
       <c r="CO131" s="27"/>
       <c r="CP131" s="17"/>
       <c r="CQ131" s="17"/>
@@ -12026,14 +12026,14 @@
       <c r="S132" s="20"/>
       <c r="T132" s="20"/>
       <c r="U132" s="20"/>
-      <c r="X132" s="20"/>
+      <c r="Y132" s="20"/>
       <c r="AB132" s="20"/>
       <c r="AC132" s="20"/>
-      <c r="AD132" s="16"/>
-      <c r="AF132" s="17"/>
-      <c r="AG132" s="25"/>
-      <c r="AH132" s="25"/>
-      <c r="AI132" s="26"/>
+      <c r="AE132" s="17"/>
+      <c r="AF132" s="25"/>
+      <c r="AG132" s="16"/>
+      <c r="AH132" s="26"/>
+      <c r="AI132" s="25"/>
       <c r="AJ132" s="16"/>
       <c r="AK132" s="16"/>
       <c r="AL132" s="16"/>
@@ -12058,7 +12058,7 @@
       <c r="BW132" s="20"/>
       <c r="BX132" s="20"/>
       <c r="BY132" s="20"/>
-      <c r="CG132" s="20"/>
+      <c r="CH132" s="20"/>
       <c r="CO132" s="27"/>
       <c r="CP132" s="17"/>
       <c r="CQ132" s="17"/>
@@ -12080,14 +12080,14 @@
       <c r="S133" s="20"/>
       <c r="T133" s="20"/>
       <c r="U133" s="20"/>
-      <c r="X133" s="20"/>
+      <c r="Y133" s="20"/>
       <c r="AB133" s="20"/>
       <c r="AC133" s="20"/>
-      <c r="AD133" s="16"/>
-      <c r="AF133" s="17"/>
-      <c r="AG133" s="25"/>
-      <c r="AH133" s="25"/>
-      <c r="AI133" s="26"/>
+      <c r="AE133" s="17"/>
+      <c r="AF133" s="25"/>
+      <c r="AG133" s="16"/>
+      <c r="AH133" s="26"/>
+      <c r="AI133" s="25"/>
       <c r="AJ133" s="16"/>
       <c r="AK133" s="16"/>
       <c r="AL133" s="16"/>
@@ -12112,7 +12112,7 @@
       <c r="BW133" s="20"/>
       <c r="BX133" s="20"/>
       <c r="BY133" s="20"/>
-      <c r="CG133" s="20"/>
+      <c r="CH133" s="20"/>
       <c r="CO133" s="27"/>
       <c r="CP133" s="17"/>
       <c r="CQ133" s="17"/>
@@ -12134,14 +12134,14 @@
       <c r="S134" s="20"/>
       <c r="T134" s="20"/>
       <c r="U134" s="20"/>
-      <c r="X134" s="20"/>
+      <c r="Y134" s="20"/>
       <c r="AB134" s="20"/>
       <c r="AC134" s="20"/>
-      <c r="AD134" s="16"/>
-      <c r="AF134" s="17"/>
-      <c r="AG134" s="25"/>
-      <c r="AH134" s="25"/>
-      <c r="AI134" s="26"/>
+      <c r="AE134" s="17"/>
+      <c r="AF134" s="25"/>
+      <c r="AG134" s="16"/>
+      <c r="AH134" s="26"/>
+      <c r="AI134" s="25"/>
       <c r="AJ134" s="16"/>
       <c r="AK134" s="16"/>
       <c r="AL134" s="16"/>
@@ -12166,7 +12166,7 @@
       <c r="BW134" s="20"/>
       <c r="BX134" s="20"/>
       <c r="BY134" s="20"/>
-      <c r="CG134" s="20"/>
+      <c r="CH134" s="20"/>
       <c r="CO134" s="27"/>
       <c r="CP134" s="17"/>
       <c r="CQ134" s="17"/>
@@ -12188,14 +12188,14 @@
       <c r="S135" s="20"/>
       <c r="T135" s="20"/>
       <c r="U135" s="20"/>
-      <c r="X135" s="20"/>
+      <c r="Y135" s="20"/>
       <c r="AB135" s="20"/>
       <c r="AC135" s="20"/>
-      <c r="AD135" s="16"/>
-      <c r="AF135" s="17"/>
-      <c r="AG135" s="25"/>
-      <c r="AH135" s="25"/>
-      <c r="AI135" s="26"/>
+      <c r="AE135" s="17"/>
+      <c r="AF135" s="25"/>
+      <c r="AG135" s="16"/>
+      <c r="AH135" s="26"/>
+      <c r="AI135" s="25"/>
       <c r="AJ135" s="16"/>
       <c r="AK135" s="16"/>
       <c r="AL135" s="16"/>
@@ -12220,7 +12220,7 @@
       <c r="BW135" s="20"/>
       <c r="BX135" s="20"/>
       <c r="BY135" s="20"/>
-      <c r="CG135" s="20"/>
+      <c r="CH135" s="20"/>
       <c r="CO135" s="27"/>
       <c r="CP135" s="17"/>
       <c r="CQ135" s="17"/>
@@ -12242,14 +12242,14 @@
       <c r="S136" s="20"/>
       <c r="T136" s="20"/>
       <c r="U136" s="20"/>
-      <c r="X136" s="20"/>
+      <c r="Y136" s="20"/>
       <c r="AB136" s="20"/>
       <c r="AC136" s="20"/>
-      <c r="AD136" s="16"/>
-      <c r="AF136" s="17"/>
-      <c r="AG136" s="25"/>
-      <c r="AH136" s="25"/>
-      <c r="AI136" s="26"/>
+      <c r="AE136" s="17"/>
+      <c r="AF136" s="25"/>
+      <c r="AG136" s="16"/>
+      <c r="AH136" s="26"/>
+      <c r="AI136" s="25"/>
       <c r="AJ136" s="16"/>
       <c r="AK136" s="16"/>
       <c r="AL136" s="16"/>
@@ -12274,7 +12274,7 @@
       <c r="BW136" s="20"/>
       <c r="BX136" s="20"/>
       <c r="BY136" s="20"/>
-      <c r="CG136" s="20"/>
+      <c r="CH136" s="20"/>
       <c r="CO136" s="27"/>
       <c r="CP136" s="17"/>
       <c r="CQ136" s="17"/>
